--- a/docs/FRONTEND_LEADER_TRACKER.xlsx
+++ b/docs/FRONTEND_LEADER_TRACKER.xlsx
@@ -131,11 +131,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
@@ -146,17 +141,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E2D5F1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
     <fill>
@@ -213,22 +213,22 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="9" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -248,6 +248,13 @@
     <xf numFmtId="9" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -267,13 +274,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -297,17 +297,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -321,7 +321,7 @@
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -333,11 +333,11 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -751,7 +751,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Last aligned to codebase: 2026-07-23 — employee and approver/team UIs are largely built with mock data; team calendar/upcoming and admin routes are still placeholders; cookie/session and live API are not wired yet.</t>
+          <t>Last aligned to codebase: 2026-07-29 — all employee, approver/team, and admin screens now have real UI with mock data; 2 minor report sub-pages still placeholders; cookie/session and live API not wired yet.</t>
         </is>
       </c>
     </row>
@@ -1877,15 +1877,15 @@
         <v>46225</v>
       </c>
       <c r="D7" s="50" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="E7" s="18">
         <f>IF(OR(C7="",D7=""),"",NETWORKDAYS(C7,D7))</f>
         <v/>
       </c>
-      <c r="F7" s="61" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="F7" s="33" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G7" s="19">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="I7" s="49" t="inlineStr">
         <is>
-          <t>Done so far: StatusBadge, FilterSelect, Pagination, LeaveTypeIconBadge, Modal, ConfirmReasonModal, AttachmentPreviewModal, and form fields. Full shared button/table kit still pending.</t>
+          <t>Built: StatusBadge, FilterSelect, Pagination, Button, Modal, ConfirmReasonModal, AttachmentPreviewModal, SuccessDialog, Skeleton, form fields, MonthYearPickerField, EmployeeMultiSelect, tableStyles, admin-specific components.</t>
         </is>
       </c>
     </row>
@@ -1917,15 +1917,15 @@
         <v>46225</v>
       </c>
       <c r="D8" s="50" t="n">
-        <v>46262</v>
+        <v>46232</v>
       </c>
       <c r="E8" s="18">
         <f>IF(OR(C8="",D8=""),"",NETWORKDAYS(C8,D8))</f>
         <v/>
       </c>
-      <c r="F8" s="61" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="F8" s="33" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G8" s="19">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="I8" s="49" t="inlineStr">
         <is>
-          <t>Real pages now cover employee + key approver/team flows. Team calendar/upcoming and all admin routes still use PagePlaceholder.</t>
+          <t>All employee, approver/team, and admin routes now have real page components. No PagePlaceholder routes remain (only 2 minor sub-reports still placeholders).</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
         <f>IF(F9="Completed",1,IF(F9="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H9" s="62">
+      <c r="H9" s="61">
         <f>IF(C9="","",C9+MOD(5-WEEKDAY(C9,2),7))</f>
         <v/>
       </c>
@@ -2012,7 +2012,7 @@
         <f>IF(F10="Completed",1,IF(F10="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H10" s="62">
+      <c r="H10" s="61">
         <f>IF(C10="","",C10+MOD(5-WEEKDAY(C10,2),7))</f>
         <v/>
       </c>
@@ -2052,7 +2052,7 @@
         <f>IF(F11="Completed",1,IF(F11="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H11" s="62">
+      <c r="H11" s="61">
         <f>IF(C11="","",C11+MOD(5-WEEKDAY(C11,2),7))</f>
         <v/>
       </c>
@@ -2092,7 +2092,7 @@
         <f>IF(F12="Completed",1,IF(F12="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H12" s="62">
+      <c r="H12" s="61">
         <f>IF(C12="","",C12+MOD(5-WEEKDAY(C12,2),7))</f>
         <v/>
       </c>
@@ -2132,7 +2132,7 @@
         <f>IF(F13="Completed",1,IF(F13="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H13" s="62">
+      <c r="H13" s="61">
         <f>IF(C13="","",C13+MOD(5-WEEKDAY(C13,2),7))</f>
         <v/>
       </c>
@@ -2172,7 +2172,7 @@
         <f>IF(F14="Completed",1,IF(F14="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H14" s="62">
+      <c r="H14" s="61">
         <f>IF(C14="","",C14+MOD(5-WEEKDAY(C14,2),7))</f>
         <v/>
       </c>
@@ -2212,7 +2212,7 @@
         <f>IF(F15="Completed",1,IF(F15="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H15" s="62">
+      <c r="H15" s="61">
         <f>IF(C15="","",C15+MOD(5-WEEKDAY(C15,2),7))</f>
         <v/>
       </c>
@@ -2252,7 +2252,7 @@
         <f>IF(F16="Completed",1,IF(F16="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H16" s="62">
+      <c r="H16" s="61">
         <f>IF(C16="","",C16+MOD(5-WEEKDAY(C16,2),7))</f>
         <v/>
       </c>
@@ -2292,7 +2292,7 @@
         <f>IF(F17="Completed",1,IF(F17="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H17" s="63">
+      <c r="H17" s="62">
         <f>IF(C17="","",C17+MOD(5-WEEKDAY(C17,2),7))</f>
         <v/>
       </c>
@@ -2332,7 +2332,7 @@
         <f>IF(F18="Completed",1,IF(F18="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H18" s="63">
+      <c r="H18" s="62">
         <f>IF(C18="","",C18+MOD(5-WEEKDAY(C18,2),7))</f>
         <v/>
       </c>
@@ -2372,7 +2372,7 @@
         <f>IF(F19="Completed",1,IF(F19="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H19" s="63">
+      <c r="H19" s="62">
         <f>IF(C19="","",C19+MOD(5-WEEKDAY(C19,2),7))</f>
         <v/>
       </c>
@@ -2412,7 +2412,7 @@
         <f>IF(F20="Completed",1,IF(F20="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H20" s="63">
+      <c r="H20" s="62">
         <f>IF(C20="","",C20+MOD(5-WEEKDAY(C20,2),7))</f>
         <v/>
       </c>
@@ -2434,29 +2434,33 @@
         </is>
       </c>
       <c r="C21" s="46" t="n">
-        <v>46252</v>
+        <v>46232</v>
       </c>
       <c r="D21" s="46" t="n">
-        <v>46255</v>
+        <v>46232</v>
       </c>
       <c r="E21" s="24">
         <f>IF(OR(C21="",D21=""),"",NETWORKDAYS(C21,D21))</f>
         <v/>
       </c>
-      <c r="F21" s="64" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="F21" s="33" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G21" s="25">
         <f>IF(F21="Completed",1,IF(F21="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H21" s="63">
+      <c r="H21" s="62">
         <f>IF(C21="","",C21+MOD(5-WEEKDAY(C21,2),7))</f>
         <v/>
       </c>
-      <c r="I21" s="45" t="inlineStr"/>
+      <c r="I21" s="45" t="inlineStr">
+        <is>
+          <t>Team Leave Calendar page (month/week views, filters, leave chips) and Upcoming Approved Leaves page are both built with mock data.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="47" t="inlineStr">
@@ -2470,29 +2474,33 @@
         </is>
       </c>
       <c r="C22" s="48" t="n">
-        <v>46252</v>
+        <v>46232</v>
       </c>
       <c r="D22" s="48" t="n">
-        <v>46255</v>
+        <v>46232</v>
       </c>
       <c r="E22" s="27">
         <f>IF(OR(C22="",D22=""),"",NETWORKDAYS(C22,D22))</f>
         <v/>
       </c>
-      <c r="F22" s="64" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="F22" s="33" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G22" s="28">
         <f>IF(F22="Completed",1,IF(F22="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H22" s="65">
+      <c r="H22" s="63">
         <f>IF(C22="","",C22+MOD(5-WEEKDAY(C22,2),7))</f>
         <v/>
       </c>
-      <c r="I22" s="47" t="inlineStr"/>
+      <c r="I22" s="47" t="inlineStr">
+        <is>
+          <t>Admin Leave Requests list (pending/all tabs, filters, search, reminders) and detail/view/validate pages are all built with mock data.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="47" t="inlineStr">
@@ -2506,29 +2514,33 @@
         </is>
       </c>
       <c r="C23" s="48" t="n">
-        <v>46254</v>
+        <v>46232</v>
       </c>
       <c r="D23" s="48" t="n">
-        <v>46259</v>
+        <v>46232</v>
       </c>
       <c r="E23" s="27">
         <f>IF(OR(C23="",D23=""),"",NETWORKDAYS(C23,D23))</f>
         <v/>
       </c>
-      <c r="F23" s="64" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="F23" s="33" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G23" s="28">
         <f>IF(F23="Completed",1,IF(F23="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H23" s="65">
+      <c r="H23" s="63">
         <f>IF(C23="","",C23+MOD(5-WEEKDAY(C23,2),7))</f>
         <v/>
       </c>
-      <c r="I23" s="47" t="inlineStr"/>
+      <c r="I23" s="47" t="inlineStr">
+        <is>
+          <t>Conversion review is handled via Admin Leave Validate page; conversion state visible on request detail/view pages.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="47" t="inlineStr">
@@ -2542,29 +2554,33 @@
         </is>
       </c>
       <c r="C24" s="48" t="n">
-        <v>46254</v>
+        <v>46232</v>
       </c>
       <c r="D24" s="48" t="n">
-        <v>46260</v>
+        <v>46232</v>
       </c>
       <c r="E24" s="27">
         <f>IF(OR(C24="",D24=""),"",NETWORKDAYS(C24,D24))</f>
         <v/>
       </c>
-      <c r="F24" s="64" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="F24" s="33" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G24" s="28">
         <f>IF(F24="Completed",1,IF(F24="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H24" s="65">
+      <c r="H24" s="63">
         <f>IF(C24="","",C24+MOD(5-WEEKDAY(C24,2),7))</f>
         <v/>
       </c>
-      <c r="I24" s="47" t="inlineStr"/>
+      <c r="I24" s="47" t="inlineStr">
+        <is>
+          <t>Admin Leave Balances page with filters, adjust-credits modal, and full distribution flows (annual, newly-regularized, parental, contractual) are built with mock data.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="47" t="inlineStr">
@@ -2578,29 +2594,33 @@
         </is>
       </c>
       <c r="C25" s="48" t="n">
-        <v>46259</v>
+        <v>46232</v>
       </c>
       <c r="D25" s="48" t="n">
-        <v>46261</v>
+        <v>46232</v>
       </c>
       <c r="E25" s="27">
         <f>IF(OR(C25="",D25=""),"",NETWORKDAYS(C25,D25))</f>
         <v/>
       </c>
-      <c r="F25" s="64" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="F25" s="33" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G25" s="28">
         <f>IF(F25="Completed",1,IF(F25="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H25" s="65">
+      <c r="H25" s="63">
         <f>IF(C25="","",C25+MOD(5-WEEKDAY(C25,2),7))</f>
         <v/>
       </c>
-      <c r="I25" s="47" t="inlineStr"/>
+      <c r="I25" s="47" t="inlineStr">
+        <is>
+          <t>Admin Administrative Log page with search, filters, month-year picker, sorting, and pagination is built with mock data.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="47" t="inlineStr">
@@ -2614,10 +2634,10 @@
         </is>
       </c>
       <c r="C26" s="48" t="n">
-        <v>46259</v>
+        <v>46232</v>
       </c>
       <c r="D26" s="48" t="n">
-        <v>46262</v>
+        <v>46232</v>
       </c>
       <c r="E26" s="27">
         <f>IF(OR(C26="",D26=""),"",NETWORKDAYS(C26,D26))</f>
@@ -2625,18 +2645,22 @@
       </c>
       <c r="F26" s="64" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G26" s="28">
         <f>IF(F26="Completed",1,IF(F26="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H26" s="65">
+      <c r="H26" s="63">
         <f>IF(C26="","",C26+MOD(5-WEEKDAY(C26,2),7))</f>
         <v/>
       </c>
-      <c r="I26" s="47" t="inlineStr"/>
+      <c r="I26" s="47" t="inlineStr">
+        <is>
+          <t>Monthly Attendance Report page built. Leave Monetization Candidates and Employees with LWOP sub-reports are still placeholders.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="47" t="inlineStr">
@@ -2653,28 +2677,28 @@
         <v>46225</v>
       </c>
       <c r="D27" s="48" t="n">
-        <v>46262</v>
+        <v>46232</v>
       </c>
       <c r="E27" s="27">
         <f>IF(OR(C27="",D27=""),"",NETWORKDAYS(C27,D27))</f>
         <v/>
       </c>
-      <c r="F27" s="61" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="F27" s="33" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G27" s="28">
         <f>IF(F27="Completed",1,IF(F27="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H27" s="65">
+      <c r="H27" s="63">
         <f>IF(C27="","",C27+MOD(5-WEEKDAY(C27,2),7))</f>
         <v/>
       </c>
       <c r="I27" s="47" t="inlineStr">
         <is>
-          <t>Employee and team filing screens support Emergency, PTB, and Maternity/Paternity options with attachment rules. Admin screens for these types are still not built.</t>
+          <t>Emergency, PTB, Maternity/Paternity handled in employee/team filing and in admin screens. Monthly attendance report covers all leave categories including LWOP.</t>
         </is>
       </c>
     </row>
@@ -2689,15 +2713,15 @@
           <t>Connect frontend to backend API (base connection and shared data types)</t>
         </is>
       </c>
-      <c r="C28" s="66" t="n">
+      <c r="C28" s="65" t="n">
         <v>46226</v>
       </c>
-      <c r="D28" s="66" t="n"/>
+      <c r="D28" s="65" t="n"/>
       <c r="E28" s="30">
         <f>IF(OR(C28="",D28=""),"",NETWORKDAYS(C28,D28))</f>
         <v/>
       </c>
-      <c r="F28" s="64" t="inlineStr">
+      <c r="F28" s="66" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -2727,15 +2751,15 @@
           <t>Use portal cookies / session to identify the user (no separate login page)</t>
         </is>
       </c>
-      <c r="C29" s="66" t="n">
+      <c r="C29" s="65" t="n">
         <v>46226</v>
       </c>
-      <c r="D29" s="66" t="n"/>
+      <c r="D29" s="65" t="n"/>
       <c r="E29" s="30">
         <f>IF(OR(C29="",D29=""),"",NETWORKDAYS(C29,D29))</f>
         <v/>
       </c>
-      <c r="F29" s="64" t="inlineStr">
+      <c r="F29" s="66" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -2765,13 +2789,13 @@
           <t>Connect employee leave screens to live API (file, history, cancel, edit)</t>
         </is>
       </c>
-      <c r="C30" s="66" t="n"/>
-      <c r="D30" s="66" t="n"/>
+      <c r="C30" s="65" t="n"/>
+      <c r="D30" s="65" t="n"/>
       <c r="E30" s="30">
         <f>IF(OR(C30="",D30=""),"",NETWORKDAYS(C30,D30))</f>
         <v/>
       </c>
-      <c r="F30" s="64" t="inlineStr">
+      <c r="F30" s="66" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -2801,13 +2825,13 @@
           <t>Connect approver / team screens to live API (inbox, approve, reject)</t>
         </is>
       </c>
-      <c r="C31" s="66" t="n"/>
-      <c r="D31" s="66" t="n"/>
+      <c r="C31" s="65" t="n"/>
+      <c r="D31" s="65" t="n"/>
       <c r="E31" s="30">
         <f>IF(OR(C31="",D31=""),"",NETWORKDAYS(C31,D31))</f>
         <v/>
       </c>
-      <c r="F31" s="64" t="inlineStr">
+      <c r="F31" s="66" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -2837,13 +2861,13 @@
           <t>Connect admin screens to live API (balances, conversion, reports)</t>
         </is>
       </c>
-      <c r="C32" s="66" t="n"/>
-      <c r="D32" s="66" t="n"/>
+      <c r="C32" s="65" t="n"/>
+      <c r="D32" s="65" t="n"/>
       <c r="E32" s="30">
         <f>IF(OR(C32="",D32=""),"",NETWORKDAYS(C32,D32))</f>
         <v/>
       </c>
-      <c r="F32" s="64" t="inlineStr">
+      <c r="F32" s="66" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -2873,13 +2897,13 @@
           <t>Joint frontend–backend smoke check once APIs are available</t>
         </is>
       </c>
-      <c r="C33" s="66" t="n"/>
-      <c r="D33" s="66" t="n"/>
+      <c r="C33" s="65" t="n"/>
+      <c r="D33" s="65" t="n"/>
       <c r="E33" s="30">
         <f>IF(OR(C33="",D33=""),"",NETWORKDAYS(C33,D33))</f>
         <v/>
       </c>
-      <c r="F33" s="64" t="inlineStr">
+      <c r="F33" s="66" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -2917,7 +2941,7 @@
         <f>IF(OR(C34="",D34=""),"",NETWORKDAYS(C34,D34))</f>
         <v/>
       </c>
-      <c r="F34" s="64" t="inlineStr">
+      <c r="F34" s="66" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -2955,7 +2979,7 @@
         <f>IF(OR(C35="",D35=""),"",NETWORKDAYS(C35,D35))</f>
         <v/>
       </c>
-      <c r="F35" s="64" t="inlineStr">
+      <c r="F35" s="66" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -2993,7 +3017,7 @@
         <f>IF(OR(C36="",D36=""),"",NETWORKDAYS(C36,D36))</f>
         <v/>
       </c>
-      <c r="F36" s="64" t="inlineStr">
+      <c r="F36" s="66" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -3031,7 +3055,7 @@
         <f>IF(OR(C37="",D37=""),"",NETWORKDAYS(C37,D37))</f>
         <v/>
       </c>
-      <c r="F37" s="64" t="inlineStr">
+      <c r="F37" s="66" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -3069,7 +3093,7 @@
         <f>IF(OR(C38="",D38=""),"",NETWORKDAYS(C38,D38))</f>
         <v/>
       </c>
-      <c r="F38" s="64" t="inlineStr">
+      <c r="F38" s="66" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -3107,7 +3131,7 @@
         <f>IF(OR(C39="",D39=""),"",NETWORKDAYS(C39,D39))</f>
         <v/>
       </c>
-      <c r="F39" s="64" t="inlineStr">
+      <c r="F39" s="66" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -3145,7 +3169,7 @@
         <f>IF(OR(C40="",D40=""),"",NETWORKDAYS(C40,D40))</f>
         <v/>
       </c>
-      <c r="F40" s="64" t="inlineStr">
+      <c r="F40" s="66" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -3183,7 +3207,7 @@
         <f>IF(OR(C41="",D41=""),"",NETWORKDAYS(C41,D41))</f>
         <v/>
       </c>
-      <c r="F41" s="64" t="inlineStr">
+      <c r="F41" s="66" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>

--- a/docs/FRONTEND_LEADER_TRACKER.xlsx
+++ b/docs/FRONTEND_LEADER_TRACKER.xlsx
@@ -13,7 +13,7 @@
     <sheet name="How to use" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Progress Tracker'!$A$1:$I$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Progress Tracker'!$A$1:$I$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -102,7 +102,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -142,6 +142,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2D5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAD1DC"/>
       </patternFill>
     </fill>
     <fill>
@@ -201,34 +206,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="7" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -269,11 +274,18 @@
     <xf numFmtId="9" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -283,15 +295,15 @@
     <xf numFmtId="9" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="10" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="10" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -307,9 +319,9 @@
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -330,22 +342,27 @@
     <xf numFmtId="165" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -715,7 +732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -751,7 +768,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Last aligned to codebase: 2026-07-29 — all employee, approver/team, and admin screens now have real UI with mock data; 2 minor report sub-pages still placeholders; cookie/session and live API not wired yet.</t>
+          <t>Last aligned to codebase: 2026-07-30 — all screens built with mock data; currently polishing CSS and layouts (section 6); cookie/session and live API not wired yet.</t>
         </is>
       </c>
     </row>
@@ -997,7 +1014,7 @@
     <row r="15">
       <c r="A15" s="29" t="inlineStr">
         <is>
-          <t>6. Backend Integration (TBD)</t>
+          <t>6. UI Polish &amp; Cleanup</t>
         </is>
       </c>
       <c r="B15" s="30">
@@ -1028,7 +1045,7 @@
     <row r="16">
       <c r="A16" s="32" t="inlineStr">
         <is>
-          <t>7. Testing (after development)</t>
+          <t>7. Backend Integration (TBD)</t>
         </is>
       </c>
       <c r="B16" s="33">
@@ -1059,7 +1076,7 @@
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>8. Documentation (after development)</t>
+          <t>8. Testing (after development)</t>
         </is>
       </c>
       <c r="B17" s="36">
@@ -1087,14 +1104,45 @@
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="38" t="inlineStr">
-        <is>
-          <t>Development progress (sections 1–5 only)</t>
-        </is>
-      </c>
-      <c r="B19" s="39">
-        <f>IF(SUM(B10:B14)=0,0,SUMPRODUCT(B10:B14,G10:G14)/SUM(B10:B14))</f>
+    <row r="18">
+      <c r="A18" s="38" t="inlineStr">
+        <is>
+          <t>9. Documentation (after development)</t>
+        </is>
+      </c>
+      <c r="B18" s="39">
+        <f>COUNTIF('Progress Tracker'!A:A,A18)</f>
+        <v/>
+      </c>
+      <c r="C18" s="39">
+        <f>COUNTIFS('Progress Tracker'!A:A,A18,'Progress Tracker'!F:F,"Completed")</f>
+        <v/>
+      </c>
+      <c r="D18" s="39">
+        <f>COUNTIFS('Progress Tracker'!A:A,A18,'Progress Tracker'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="E18" s="39">
+        <f>COUNTIFS('Progress Tracker'!A:A,A18,'Progress Tracker'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="F18" s="39">
+        <f>COUNTIFS('Progress Tracker'!A:A,A18,'Progress Tracker'!F:F,"Blocked")</f>
+        <v/>
+      </c>
+      <c r="G18" s="40">
+        <f>IF(B18=0,0,(C18+0.5*D18)/B18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="41" t="inlineStr">
+        <is>
+          <t>Development progress (sections 1–6 only)</t>
+        </is>
+      </c>
+      <c r="B20" s="42">
+        <f>IF(SUM(B10:B15)=0,0,SUMPRODUCT(B10:B15,G10:G15)/SUM(B10:B15))</f>
         <v/>
       </c>
     </row>
@@ -1106,7 +1154,7 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
-  <conditionalFormatting sqref="G10:G17">
+  <conditionalFormatting sqref="G10:G18">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1128,7 +1176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1154,449 +1202,513 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="40" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>Phase</t>
         </is>
       </c>
-      <c r="B4" s="40" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="C4" s="40" t="inlineStr">
+      <c r="C4" s="43" t="inlineStr">
         <is>
           <t>End Date</t>
         </is>
       </c>
-      <c r="D4" s="40" t="inlineStr">
+      <c r="D4" s="43" t="inlineStr">
         <is>
           <t>Days (weekdays)</t>
         </is>
       </c>
-      <c r="E4" s="40" t="inlineStr">
+      <c r="E4" s="43" t="inlineStr">
         <is>
           <t>Focus</t>
         </is>
       </c>
-      <c r="F4" s="40" t="inlineStr">
+      <c r="F4" s="43" t="inlineStr">
         <is>
           <t>Weekly Date</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="41" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>Phase 1 — Foundation (development)</t>
         </is>
       </c>
-      <c r="B5" s="42" t="n">
+      <c r="B5" s="45" t="n">
         <v>46224</v>
       </c>
-      <c r="C5" s="42" t="n">
+      <c r="C5" s="45" t="n">
         <v>46233</v>
       </c>
       <c r="D5" s="15">
         <f>NETWORKDAYS(B5,C5)</f>
         <v/>
       </c>
-      <c r="E5" s="41" t="inlineStr">
-        <is>
-          <t>Project setup, layout, menus, reusable UI.</t>
-        </is>
-      </c>
-      <c r="F5" s="42">
+      <c r="E5" s="44" t="inlineStr">
+        <is>
+          <t>Project setup, layout, collapsible sidebar, menus, reusable UI.</t>
+        </is>
+      </c>
+      <c r="F5" s="45">
         <f>B5+MOD(5-WEEKDAY(B5,2),7)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>Phase 2 — Employee features (development)</t>
         </is>
       </c>
-      <c r="B6" s="44" t="n">
+      <c r="B6" s="47" t="n">
         <v>46231</v>
       </c>
-      <c r="C6" s="44" t="n">
+      <c r="C6" s="47" t="n">
         <v>46247</v>
       </c>
       <c r="D6" s="21">
         <f>NETWORKDAYS(B6,C6)</f>
         <v/>
       </c>
-      <c r="E6" s="43" t="inlineStr">
+      <c r="E6" s="46" t="inlineStr">
         <is>
           <t>Dashboard, file leave, request details, history, edit, and cancel.</t>
         </is>
       </c>
-      <c r="F6" s="44">
+      <c r="F6" s="47">
         <f>B6+MOD(5-WEEKDAY(B6,2),7)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="45" t="inlineStr">
+      <c r="A7" s="48" t="inlineStr">
         <is>
           <t>Phase 3 — Approver / team (development)</t>
         </is>
       </c>
-      <c r="B7" s="46" t="n">
+      <c r="B7" s="49" t="n">
         <v>46245</v>
       </c>
-      <c r="C7" s="46" t="n">
+      <c r="C7" s="49" t="n">
         <v>46255</v>
       </c>
       <c r="D7" s="24">
         <f>NETWORKDAYS(B7,C7)</f>
         <v/>
       </c>
-      <c r="E7" s="45" t="inlineStr">
+      <c r="E7" s="48" t="inlineStr">
         <is>
           <t>Approvals inbox, approve/reject, file for member, team calendar.</t>
         </is>
       </c>
-      <c r="F7" s="46">
+      <c r="F7" s="49">
         <f>B7+MOD(5-WEEKDAY(B7,2),7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>Phase 4 — Admin features (development)</t>
         </is>
       </c>
-      <c r="B8" s="48" t="n">
+      <c r="B8" s="51" t="n">
         <v>46252</v>
       </c>
-      <c r="C8" s="48" t="n">
+      <c r="C8" s="51" t="n">
         <v>46262</v>
       </c>
       <c r="D8" s="27">
         <f>NETWORKDAYS(B8,C8)</f>
         <v/>
       </c>
-      <c r="E8" s="47" t="inlineStr">
-        <is>
-          <t>Admin requests, conversion review, balances, logs, and reports.</t>
-        </is>
-      </c>
-      <c r="F8" s="48">
+      <c r="E8" s="50" t="inlineStr">
+        <is>
+          <t>Admin requests, conversion review, balances, logs, and all three reports (UI complete ahead of schedule).</t>
+        </is>
+      </c>
+      <c r="F8" s="51">
         <f>B8+MOD(5-WEEKDAY(B8,2),7)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="49" t="inlineStr">
-        <is>
-          <t>Phase 5 — Development complete (commitment)</t>
-        </is>
-      </c>
-      <c r="B9" s="50" t="n">
-        <v>46262</v>
-      </c>
-      <c r="C9" s="50" t="n">
-        <v>46265</v>
+      <c r="A9" s="52" t="inlineStr">
+        <is>
+          <t>Phase 5 — UI polish &amp; cleanup (development)</t>
+        </is>
+      </c>
+      <c r="B9" s="53" t="n">
+        <v>46233</v>
+      </c>
+      <c r="C9" s="53" t="n">
+        <v>46249</v>
       </c>
       <c r="D9" s="18">
         <f>NETWORKDAYS(B9,C9)</f>
         <v/>
       </c>
-      <c r="E9" s="49" t="inlineStr">
+      <c r="E9" s="52" t="inlineStr">
+        <is>
+          <t>CSS review, layout checks, and consistent spacing across screens.</t>
+        </is>
+      </c>
+      <c r="F9" s="53">
+        <f>B9+MOD(5-WEEKDAY(B9,2),7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="44" t="inlineStr">
+        <is>
+          <t>Phase 6 — Development complete (commitment)</t>
+        </is>
+      </c>
+      <c r="B10" s="45" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C10" s="45" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D10" s="15">
+        <f>NETWORKDAYS(B10,C10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="44" t="inlineStr">
         <is>
           <t>Frontend development screens targeted complete. End of August = development only.</t>
         </is>
       </c>
-      <c r="F9" s="50">
-        <f>B9+MOD(5-WEEKDAY(B9,2),7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="51" t="inlineStr">
+      <c r="F10" s="45">
+        <f>B10+MOD(5-WEEKDAY(B10,2),7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="54" t="inlineStr">
         <is>
           <t>After / alongside development (no fixed end dates yet)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="52" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="55" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B13" s="52" t="inlineStr">
+      <c r="B14" s="55" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="53" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="56" t="inlineStr">
         <is>
           <t>Backend integration (parallel / TBD)</t>
         </is>
       </c>
-      <c r="B14" s="53" t="inlineStr">
+      <c r="B15" s="56" t="inlineStr">
         <is>
           <t>Ongoing with backend partner — no fixed day count yet. Update when APIs and cookie/session are ready.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="54" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="57" t="inlineStr">
         <is>
           <t>Testing (after development)</t>
         </is>
       </c>
-      <c r="B15" s="54" t="inlineStr">
+      <c r="B16" s="57" t="inlineStr">
         <is>
           <t>Planned to start on/after 2026-09-01. End date TBD.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="55" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="58" t="inlineStr">
         <is>
           <t>Documentation (after development)</t>
         </is>
       </c>
-      <c r="B16" s="55" t="inlineStr">
+      <c r="B17" s="58" t="inlineStr">
         <is>
           <t>Planned to start on/after 2026-09-01. End date TBD.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="51" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="54" t="inlineStr">
         <is>
           <t>Key milestones (development)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="52" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="55" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="B20" s="52" t="inlineStr">
+      <c r="B21" s="55" t="inlineStr">
         <is>
           <t>Target Date</t>
         </is>
       </c>
-      <c r="C20" s="52" t="inlineStr">
+      <c r="C21" s="55" t="inlineStr">
         <is>
           <t>Weekly Date</t>
         </is>
       </c>
-      <c r="D20" s="52" t="inlineStr">
+      <c r="D21" s="55" t="inlineStr">
         <is>
           <t>Related section</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="56" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="59" t="inlineStr">
         <is>
           <t>App shell &amp; menus ready (dev kickoff)</t>
         </is>
       </c>
-      <c r="B21" s="57" t="n">
+      <c r="B22" s="60" t="n">
         <v>46225</v>
       </c>
-      <c r="C21" s="57">
-        <f>B21+MOD(5-WEEKDAY(B21,2),7)</f>
-        <v/>
-      </c>
-      <c r="D21" s="56" t="inlineStr">
+      <c r="C22" s="60">
+        <f>B22+MOD(5-WEEKDAY(B22,2),7)</f>
+        <v/>
+      </c>
+      <c r="D22" s="59" t="inlineStr">
         <is>
           <t>2. Core App Shell</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="56" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="59" t="inlineStr">
         <is>
           <t>Reusable UI + employee screens underway</t>
         </is>
       </c>
-      <c r="B22" s="57" t="n">
+      <c r="B23" s="60" t="n">
         <v>46234</v>
       </c>
-      <c r="C22" s="57">
-        <f>B22+MOD(5-WEEKDAY(B22,2),7)</f>
-        <v/>
-      </c>
-      <c r="D22" s="56" t="inlineStr">
+      <c r="C23" s="60">
+        <f>B23+MOD(5-WEEKDAY(B23,2),7)</f>
+        <v/>
+      </c>
+      <c r="D23" s="59" t="inlineStr">
         <is>
           <t>2–3</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="56" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="59" t="inlineStr">
         <is>
           <t>Employee filing &amp; history usable (UI)</t>
         </is>
       </c>
-      <c r="B23" s="57" t="n">
+      <c r="B24" s="60" t="n">
         <v>46247</v>
       </c>
-      <c r="C23" s="57">
-        <f>B23+MOD(5-WEEKDAY(B23,2),7)</f>
-        <v/>
-      </c>
-      <c r="D23" s="56" t="inlineStr">
+      <c r="C24" s="60">
+        <f>B24+MOD(5-WEEKDAY(B24,2),7)</f>
+        <v/>
+      </c>
+      <c r="D24" s="59" t="inlineStr">
         <is>
           <t>3. Employee Features</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="56" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="59" t="inlineStr">
         <is>
           <t>Approver approve/reject usable (UI)</t>
         </is>
       </c>
-      <c r="B24" s="57" t="n">
+      <c r="B25" s="60" t="n">
         <v>46252</v>
       </c>
-      <c r="C24" s="57">
-        <f>B24+MOD(5-WEEKDAY(B24,2),7)</f>
-        <v/>
-      </c>
-      <c r="D24" s="56" t="inlineStr">
+      <c r="C25" s="60">
+        <f>B25+MOD(5-WEEKDAY(B25,2),7)</f>
+        <v/>
+      </c>
+      <c r="D25" s="59" t="inlineStr">
         <is>
           <t>4. Approver / Team</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="56" t="inlineStr">
-        <is>
-          <t>Admin screens usable (UI)</t>
-        </is>
-      </c>
-      <c r="B25" s="57" t="n">
+    <row r="26">
+      <c r="A26" s="59" t="inlineStr">
+        <is>
+          <t>Admin screens usable (UI) — done early</t>
+        </is>
+      </c>
+      <c r="B26" s="60" t="n">
+        <v>46233</v>
+      </c>
+      <c r="C26" s="60">
+        <f>B26+MOD(5-WEEKDAY(B26,2),7)</f>
+        <v/>
+      </c>
+      <c r="D26" s="59" t="inlineStr">
+        <is>
+          <t>5. Admin Features</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="59" t="inlineStr">
+        <is>
+          <t>Admin screens target (original plan)</t>
+        </is>
+      </c>
+      <c r="B27" s="60" t="n">
         <v>46262</v>
       </c>
-      <c r="C25" s="57">
-        <f>B25+MOD(5-WEEKDAY(B25,2),7)</f>
-        <v/>
-      </c>
-      <c r="D25" s="56" t="inlineStr">
+      <c r="C27" s="60">
+        <f>B27+MOD(5-WEEKDAY(B27,2),7)</f>
+        <v/>
+      </c>
+      <c r="D27" s="59" t="inlineStr">
         <is>
           <t>5. Admin Features</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="56" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="59" t="inlineStr">
+        <is>
+          <t>UI polish &amp; layout cleanup underway</t>
+        </is>
+      </c>
+      <c r="B28" s="60" t="n">
+        <v>46233</v>
+      </c>
+      <c r="C28" s="60">
+        <f>B28+MOD(5-WEEKDAY(B28,2),7)</f>
+        <v/>
+      </c>
+      <c r="D28" s="59" t="inlineStr">
+        <is>
+          <t>6. UI Polish &amp; Cleanup</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="59" t="inlineStr">
         <is>
           <t>Development complete (August commitment)</t>
         </is>
       </c>
-      <c r="B26" s="57" t="n">
+      <c r="B29" s="60" t="n">
         <v>46265</v>
       </c>
-      <c r="C26" s="57">
-        <f>B26+MOD(5-WEEKDAY(B26,2),7)</f>
-        <v/>
-      </c>
-      <c r="D26" s="56" t="inlineStr">
-        <is>
-          <t>Sections 1–5</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="51" t="inlineStr">
+      <c r="C29" s="60">
+        <f>B29+MOD(5-WEEKDAY(B29,2),7)</f>
+        <v/>
+      </c>
+      <c r="D29" s="59" t="inlineStr">
+        <is>
+          <t>Sections 1–6</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="54" t="inlineStr">
         <is>
           <t>Weekly checkpoints (Fridays) — development</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="52" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="55" t="inlineStr">
         <is>
           <t>Week ending (Friday)</t>
         </is>
       </c>
-      <c r="B30" s="52" t="inlineStr">
+      <c r="B33" s="55" t="inlineStr">
         <is>
           <t>What leaders should expect to see</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="57" t="n">
+    <row r="34">
+      <c r="A34" s="60" t="n">
         <v>46227</v>
       </c>
-      <c r="B31" s="56" t="inlineStr">
+      <c r="B34" s="59" t="inlineStr">
         <is>
           <t>Kickoff: layout/menus; align cookie/session &amp; API approach with backend</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="57" t="n">
+    <row r="35">
+      <c r="A35" s="60" t="n">
         <v>46234</v>
       </c>
-      <c r="B32" s="56" t="inlineStr">
-        <is>
-          <t>Reusable UI started; employee screens beginning</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="57" t="n">
+      <c r="B35" s="59" t="inlineStr">
+        <is>
+          <t>Reusable UI done; employee + approver + admin screens largely complete (ahead of plan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="60" t="n">
         <v>46241</v>
       </c>
-      <c r="B33" s="56" t="inlineStr">
-        <is>
-          <t>Employee dashboard and file-leave UI in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="57" t="n">
+      <c r="B36" s="59" t="inlineStr">
+        <is>
+          <t>CSS and layout cleanup in progress across screens</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="60" t="n">
         <v>46248</v>
       </c>
-      <c r="B34" s="56" t="inlineStr">
-        <is>
-          <t>Employee UI largely complete; approver screens started</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="57" t="n">
+      <c r="B37" s="59" t="inlineStr">
+        <is>
+          <t>Layout polish wrapping up; ready for backend hookup when APIs are available</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="60" t="n">
         <v>46255</v>
       </c>
-      <c r="B35" s="56" t="inlineStr">
+      <c r="B38" s="59" t="inlineStr">
         <is>
           <t>Approver UI in place; admin screens underway</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="57" t="n">
+    <row r="39">
+      <c r="A39" s="60" t="n">
         <v>46262</v>
       </c>
-      <c r="B36" s="56" t="inlineStr">
+      <c r="B39" s="59" t="inlineStr">
         <is>
           <t>Admin UI in progress / wrapping up</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="57" t="n">
+    <row r="40">
+      <c r="A40" s="60" t="n">
         <v>46265</v>
       </c>
-      <c r="B37" s="56" t="inlineStr">
+      <c r="B40" s="59" t="inlineStr">
         <is>
           <t>Target: frontend DEVELOPMENT complete (not testing/docs)</t>
         </is>
@@ -1617,7 +1729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1632,74 +1744,74 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="61" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="B1" s="58" t="inlineStr">
+      <c r="B1" s="61" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="C1" s="58" t="inlineStr">
+      <c r="C1" s="61" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="D1" s="58" t="inlineStr">
+      <c r="D1" s="61" t="inlineStr">
         <is>
           <t>End Date</t>
         </is>
       </c>
-      <c r="E1" s="58" t="inlineStr">
+      <c r="E1" s="61" t="inlineStr">
         <is>
           <t>Days (weekdays)</t>
         </is>
       </c>
-      <c r="F1" s="58" t="inlineStr">
+      <c r="F1" s="61" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="58" t="inlineStr">
+      <c r="G1" s="61" t="inlineStr">
         <is>
           <t>Progress %</t>
         </is>
       </c>
-      <c r="H1" s="58" t="inlineStr">
+      <c r="H1" s="61" t="inlineStr">
         <is>
           <t>Weekly Date</t>
         </is>
       </c>
-      <c r="I1" s="58" t="inlineStr">
+      <c r="I1" s="61" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="41" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>1. Project Setup</t>
         </is>
       </c>
-      <c r="B2" s="41" t="inlineStr">
+      <c r="B2" s="44" t="inlineStr">
         <is>
           <t>Set up frontend project (React, TypeScript, styling tools)</t>
         </is>
       </c>
-      <c r="C2" s="42" t="n">
+      <c r="C2" s="45" t="n">
         <v>46224</v>
       </c>
-      <c r="D2" s="42" t="n">
+      <c r="D2" s="45" t="n">
         <v>46224</v>
       </c>
       <c r="E2" s="15">
         <f>IF(OR(C2="",D2=""),"",NETWORKDAYS(C2,D2))</f>
         <v/>
       </c>
-      <c r="F2" s="33" t="inlineStr">
+      <c r="F2" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -1708,34 +1820,34 @@
         <f>IF(F2="Completed",1,IF(F2="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H2" s="59">
+      <c r="H2" s="62">
         <f>IF(C2="","",C2+MOD(5-WEEKDAY(C2,2),7))</f>
         <v/>
       </c>
-      <c r="I2" s="41" t="inlineStr"/>
+      <c r="I2" s="44" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="44" t="inlineStr">
         <is>
           <t>1. Project Setup</t>
         </is>
       </c>
-      <c r="B3" s="41" t="inlineStr">
+      <c r="B3" s="44" t="inlineStr">
         <is>
           <t>Apply brand colors, fonts, and base page styles</t>
         </is>
       </c>
-      <c r="C3" s="42" t="n">
+      <c r="C3" s="45" t="n">
         <v>46224</v>
       </c>
-      <c r="D3" s="42" t="n">
+      <c r="D3" s="45" t="n">
         <v>46225</v>
       </c>
       <c r="E3" s="15">
         <f>IF(OR(C3="",D3=""),"",NETWORKDAYS(C3,D3))</f>
         <v/>
       </c>
-      <c r="F3" s="33" t="inlineStr">
+      <c r="F3" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -1744,34 +1856,34 @@
         <f>IF(F3="Completed",1,IF(F3="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H3" s="59">
+      <c r="H3" s="62">
         <f>IF(C3="","",C3+MOD(5-WEEKDAY(C3,2),7))</f>
         <v/>
       </c>
-      <c r="I3" s="41" t="inlineStr"/>
+      <c r="I3" s="44" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="41" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>1. Project Setup</t>
         </is>
       </c>
-      <c r="B4" s="41" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>Define page routes for Employee, Approver, and Admin areas</t>
         </is>
       </c>
-      <c r="C4" s="42" t="n">
+      <c r="C4" s="45" t="n">
         <v>46224</v>
       </c>
-      <c r="D4" s="42" t="n">
+      <c r="D4" s="45" t="n">
         <v>46225</v>
       </c>
       <c r="E4" s="15">
         <f>IF(OR(C4="",D4=""),"",NETWORKDAYS(C4,D4))</f>
         <v/>
       </c>
-      <c r="F4" s="33" t="inlineStr">
+      <c r="F4" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -1780,34 +1892,34 @@
         <f>IF(F4="Completed",1,IF(F4="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H4" s="59">
+      <c r="H4" s="62">
         <f>IF(C4="","",C4+MOD(5-WEEKDAY(C4,2),7))</f>
         <v/>
       </c>
-      <c r="I4" s="41" t="inlineStr"/>
+      <c r="I4" s="44" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="49" t="inlineStr">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t>2. Core App Shell</t>
         </is>
       </c>
-      <c r="B5" s="49" t="inlineStr">
+      <c r="B5" s="52" t="inlineStr">
         <is>
           <t>Build main app layout (sidebar menu and top header)</t>
         </is>
       </c>
-      <c r="C5" s="50" t="n">
+      <c r="C5" s="53" t="n">
         <v>46224</v>
       </c>
-      <c r="D5" s="50" t="n">
+      <c r="D5" s="53" t="n">
         <v>46225</v>
       </c>
       <c r="E5" s="18">
         <f>IF(OR(C5="",D5=""),"",NETWORKDAYS(C5,D5))</f>
         <v/>
       </c>
-      <c r="F5" s="33" t="inlineStr">
+      <c r="F5" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -1816,34 +1928,34 @@
         <f>IF(F5="Completed",1,IF(F5="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H5" s="60">
+      <c r="H5" s="63">
         <f>IF(C5="","",C5+MOD(5-WEEKDAY(C5,2),7))</f>
         <v/>
       </c>
-      <c r="I5" s="49" t="inlineStr"/>
+      <c r="I5" s="52" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="49" t="inlineStr">
+      <c r="A6" s="52" t="inlineStr">
         <is>
           <t>2. Core App Shell</t>
         </is>
       </c>
-      <c r="B6" s="49" t="inlineStr">
+      <c r="B6" s="52" t="inlineStr">
         <is>
           <t>Show different menus based on user role (Employee / Approver / Admin)</t>
         </is>
       </c>
-      <c r="C6" s="50" t="n">
+      <c r="C6" s="53" t="n">
         <v>46224</v>
       </c>
-      <c r="D6" s="50" t="n">
+      <c r="D6" s="53" t="n">
         <v>46225</v>
       </c>
       <c r="E6" s="18">
         <f>IF(OR(C6="",D6=""),"",NETWORKDAYS(C6,D6))</f>
         <v/>
       </c>
-      <c r="F6" s="33" t="inlineStr">
+      <c r="F6" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -1852,38 +1964,38 @@
         <f>IF(F6="Completed",1,IF(F6="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H6" s="60">
+      <c r="H6" s="63">
         <f>IF(C6="","",C6+MOD(5-WEEKDAY(C6,2),7))</f>
         <v/>
       </c>
-      <c r="I6" s="49" t="inlineStr">
+      <c r="I6" s="52" t="inlineStr">
         <is>
           <t>Role-based sidebar works. Dev-only role preview remains until portal cookies/session are wired.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="49" t="inlineStr">
+      <c r="A7" s="52" t="inlineStr">
         <is>
           <t>2. Core App Shell</t>
         </is>
       </c>
-      <c r="B7" s="49" t="inlineStr">
+      <c r="B7" s="52" t="inlineStr">
         <is>
           <t>Create reusable screen parts (buttons, forms, tables, status labels)</t>
         </is>
       </c>
-      <c r="C7" s="50" t="n">
+      <c r="C7" s="53" t="n">
         <v>46225</v>
       </c>
-      <c r="D7" s="50" t="n">
-        <v>46232</v>
+      <c r="D7" s="53" t="n">
+        <v>46233</v>
       </c>
       <c r="E7" s="18">
         <f>IF(OR(C7="",D7=""),"",NETWORKDAYS(C7,D7))</f>
         <v/>
       </c>
-      <c r="F7" s="33" t="inlineStr">
+      <c r="F7" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -1892,38 +2004,38 @@
         <f>IF(F7="Completed",1,IF(F7="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H7" s="60">
+      <c r="H7" s="63">
         <f>IF(C7="","",C7+MOD(5-WEEKDAY(C7,2),7))</f>
         <v/>
       </c>
-      <c r="I7" s="49" t="inlineStr">
-        <is>
-          <t>Built: StatusBadge, FilterSelect, Pagination, Button, Modal, ConfirmReasonModal, AttachmentPreviewModal, SuccessDialog, Skeleton, form fields, MonthYearPickerField, EmployeeMultiSelect, tableStyles, admin-specific components.</t>
+      <c r="I7" s="52" t="inlineStr">
+        <is>
+          <t>Built: StatusBadge, FilterSelect, Pagination, Button, Modal, ConfirmReasonModal, AttachmentPreviewModal, SuccessDialog, Skeleton, form fields, MonthYearPickerField, YearPickerField, EmployeeMultiSelect, tableStyles, admin-specific components.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="49" t="inlineStr">
+      <c r="A8" s="52" t="inlineStr">
         <is>
           <t>2. Core App Shell</t>
         </is>
       </c>
-      <c r="B8" s="49" t="inlineStr">
-        <is>
-          <t>Replace temporary placeholder pages with real screens</t>
-        </is>
-      </c>
-      <c r="C8" s="50" t="n">
-        <v>46225</v>
-      </c>
-      <c r="D8" s="50" t="n">
+      <c r="B8" s="52" t="inlineStr">
+        <is>
+          <t>Collapsible sidebar menu with saved user preference</t>
+        </is>
+      </c>
+      <c r="C8" s="53" t="n">
         <v>46232</v>
+      </c>
+      <c r="D8" s="53" t="n">
+        <v>46233</v>
       </c>
       <c r="E8" s="18">
         <f>IF(OR(C8="",D8=""),"",NETWORKDAYS(C8,D8))</f>
         <v/>
       </c>
-      <c r="F8" s="33" t="inlineStr">
+      <c r="F8" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -1932,78 +2044,78 @@
         <f>IF(F8="Completed",1,IF(F8="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H8" s="60">
+      <c r="H8" s="63">
         <f>IF(C8="","",C8+MOD(5-WEEKDAY(C8,2),7))</f>
         <v/>
       </c>
-      <c r="I8" s="49" t="inlineStr">
-        <is>
-          <t>All employee, approver/team, and admin routes now have real page components. No PagePlaceholder routes remain (only 2 minor sub-reports still placeholders).</t>
+      <c r="I8" s="52" t="inlineStr">
+        <is>
+          <t>Sidebar collapses to icon-only mode with flyout submenus, tooltips, and localStorage preference. Top header toggle wired in AppLayout.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="43" t="inlineStr">
+      <c r="A9" s="52" t="inlineStr">
+        <is>
+          <t>2. Core App Shell</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="inlineStr">
+        <is>
+          <t>Replace temporary placeholder pages with real screens</t>
+        </is>
+      </c>
+      <c r="C9" s="53" t="n">
+        <v>46225</v>
+      </c>
+      <c r="D9" s="53" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E9" s="18">
+        <f>IF(OR(C9="",D9=""),"",NETWORKDAYS(C9,D9))</f>
+        <v/>
+      </c>
+      <c r="F9" s="36" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G9" s="19">
+        <f>IF(F9="Completed",1,IF(F9="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H9" s="63">
+        <f>IF(C9="","",C9+MOD(5-WEEKDAY(C9,2),7))</f>
+        <v/>
+      </c>
+      <c r="I9" s="52" t="inlineStr">
+        <is>
+          <t>All employee, approver/team, and admin routes now have real page components. PagePlaceholder is no longer used in routing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="46" t="inlineStr">
         <is>
           <t>3. Employee Features</t>
         </is>
       </c>
-      <c r="B9" s="43" t="inlineStr">
+      <c r="B10" s="46" t="inlineStr">
         <is>
           <t>Employee dashboard: leave balances and recent requests</t>
         </is>
       </c>
-      <c r="C9" s="44" t="n">
+      <c r="C10" s="47" t="n">
         <v>46225</v>
       </c>
-      <c r="D9" s="44" t="n">
+      <c r="D10" s="47" t="n">
         <v>46225</v>
-      </c>
-      <c r="E9" s="21">
-        <f>IF(OR(C9="",D9=""),"",NETWORKDAYS(C9,D9))</f>
-        <v/>
-      </c>
-      <c r="F9" s="33" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="G9" s="22">
-        <f>IF(F9="Completed",1,IF(F9="In Progress",0.5,0))</f>
-        <v/>
-      </c>
-      <c r="H9" s="61">
-        <f>IF(C9="","",C9+MOD(5-WEEKDAY(C9,2),7))</f>
-        <v/>
-      </c>
-      <c r="I9" s="43" t="inlineStr">
-        <is>
-          <t>UI complete (balances, reserved credits, filters, pagination). Uses mock data until Backend Integration.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="43" t="inlineStr">
-        <is>
-          <t>3. Employee Features</t>
-        </is>
-      </c>
-      <c r="B10" s="43" t="inlineStr">
-        <is>
-          <t>File leave request (dates, leave type, reason, attachment)</t>
-        </is>
-      </c>
-      <c r="C10" s="44" t="n">
-        <v>46226</v>
-      </c>
-      <c r="D10" s="44" t="n">
-        <v>46226</v>
       </c>
       <c r="E10" s="21">
         <f>IF(OR(C10="",D10=""),"",NETWORKDAYS(C10,D10))</f>
         <v/>
       </c>
-      <c r="F10" s="33" t="inlineStr">
+      <c r="F10" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2012,38 +2124,38 @@
         <f>IF(F10="Completed",1,IF(F10="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H10" s="61">
+      <c r="H10" s="64">
         <f>IF(C10="","",C10+MOD(5-WEEKDAY(C10,2),7))</f>
         <v/>
       </c>
-      <c r="I10" s="43" t="inlineStr">
-        <is>
-          <t>Apply Leave page is built with employee info, leave type/day type, date range, reason, attachment rules, duration preview, confirm modal, and success dialog. Uses mock submit until Backend Integration.</t>
+      <c r="I10" s="46" t="inlineStr">
+        <is>
+          <t>UI complete (balances, reserved credits, filters, pagination). Uses mock data until Backend Integration.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="46" t="inlineStr">
         <is>
           <t>3. Employee Features</t>
         </is>
       </c>
-      <c r="B11" s="43" t="inlineStr">
-        <is>
-          <t>Show unpaid leave (LWOP) warning when credits are not enough</t>
-        </is>
-      </c>
-      <c r="C11" s="44" t="n">
+      <c r="B11" s="46" t="inlineStr">
+        <is>
+          <t>File leave request (dates, leave type, reason, attachment)</t>
+        </is>
+      </c>
+      <c r="C11" s="47" t="n">
         <v>46226</v>
       </c>
-      <c r="D11" s="44" t="n">
+      <c r="D11" s="47" t="n">
         <v>46226</v>
       </c>
       <c r="E11" s="21">
         <f>IF(OR(C11="",D11=""),"",NETWORKDAYS(C11,D11))</f>
         <v/>
       </c>
-      <c r="F11" s="33" t="inlineStr">
+      <c r="F11" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2052,38 +2164,38 @@
         <f>IF(F11="Completed",1,IF(F11="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H11" s="61">
+      <c r="H11" s="64">
         <f>IF(C11="","",C11+MOD(5-WEEKDAY(C11,2),7))</f>
         <v/>
       </c>
-      <c r="I11" s="43" t="inlineStr">
-        <is>
-          <t>LWOP / remaining-balance warning is shown in filing forms using mock remaining-day logic.</t>
+      <c r="I11" s="46" t="inlineStr">
+        <is>
+          <t>Apply Leave page is built with employee info, leave type/day type, date range, reason, attachment rules, duration preview, confirm modal, and success dialog. Uses mock submit until Backend Integration.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="46" t="inlineStr">
         <is>
           <t>3. Employee Features</t>
         </is>
       </c>
-      <c r="B12" s="43" t="inlineStr">
-        <is>
-          <t>Leave request details: status, approvals needed, and activity history</t>
-        </is>
-      </c>
-      <c r="C12" s="44" t="n">
-        <v>46225</v>
-      </c>
-      <c r="D12" s="44" t="n">
-        <v>46225</v>
+      <c r="B12" s="46" t="inlineStr">
+        <is>
+          <t>Show unpaid leave (LWOP) warning when credits are not enough</t>
+        </is>
+      </c>
+      <c r="C12" s="47" t="n">
+        <v>46226</v>
+      </c>
+      <c r="D12" s="47" t="n">
+        <v>46226</v>
       </c>
       <c r="E12" s="21">
         <f>IF(OR(C12="",D12=""),"",NETWORKDAYS(C12,D12))</f>
         <v/>
       </c>
-      <c r="F12" s="33" t="inlineStr">
+      <c r="F12" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2092,38 +2204,38 @@
         <f>IF(F12="Completed",1,IF(F12="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H12" s="61">
+      <c r="H12" s="64">
         <f>IF(C12="","",C12+MOD(5-WEEKDAY(C12,2),7))</f>
         <v/>
       </c>
-      <c r="I12" s="43" t="inlineStr">
-        <is>
-          <t>UI complete: leave info, approval progress/requirements, approver list, attachments, conversion view. Mock data; activity timeline not a separate log yet.</t>
+      <c r="I12" s="46" t="inlineStr">
+        <is>
+          <t>LWOP / remaining-balance warning is shown in filing forms using mock remaining-day logic.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="A13" s="46" t="inlineStr">
         <is>
           <t>3. Employee Features</t>
         </is>
       </c>
-      <c r="B13" s="43" t="inlineStr">
-        <is>
-          <t>Activity log / leave history with filters</t>
-        </is>
-      </c>
-      <c r="C13" s="44" t="n">
-        <v>46226</v>
-      </c>
-      <c r="D13" s="44" t="n">
-        <v>46226</v>
+      <c r="B13" s="46" t="inlineStr">
+        <is>
+          <t>Leave request details: status, approvals needed, and activity history</t>
+        </is>
+      </c>
+      <c r="C13" s="47" t="n">
+        <v>46225</v>
+      </c>
+      <c r="D13" s="47" t="n">
+        <v>46225</v>
       </c>
       <c r="E13" s="21">
         <f>IF(OR(C13="",D13=""),"",NETWORKDAYS(C13,D13))</f>
         <v/>
       </c>
-      <c r="F13" s="33" t="inlineStr">
+      <c r="F13" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2132,38 +2244,38 @@
         <f>IF(F13="Completed",1,IF(F13="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H13" s="61">
+      <c r="H13" s="64">
         <f>IF(C13="","",C13+MOD(5-WEEKDAY(C13,2),7))</f>
         <v/>
       </c>
-      <c r="I13" s="43" t="inlineStr">
-        <is>
-          <t>Activity Log page exists with filtering, sorting, pagination, and mock activity data.</t>
+      <c r="I13" s="46" t="inlineStr">
+        <is>
+          <t>UI complete: leave info, approval progress/requirements, approver list, attachments, conversion view. Mock data; activity timeline not a separate log yet.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="46" t="inlineStr">
         <is>
           <t>3. Employee Features</t>
         </is>
       </c>
-      <c r="B14" s="43" t="inlineStr">
-        <is>
-          <t>Edit leave request (only while still waiting for first approval)</t>
-        </is>
-      </c>
-      <c r="C14" s="44" t="n">
-        <v>46225</v>
-      </c>
-      <c r="D14" s="44" t="n">
-        <v>46247</v>
+      <c r="B14" s="46" t="inlineStr">
+        <is>
+          <t>Activity log / leave history with filters</t>
+        </is>
+      </c>
+      <c r="C14" s="47" t="n">
+        <v>46226</v>
+      </c>
+      <c r="D14" s="47" t="n">
+        <v>46226</v>
       </c>
       <c r="E14" s="21">
         <f>IF(OR(C14="",D14=""),"",NETWORKDAYS(C14,D14))</f>
         <v/>
       </c>
-      <c r="F14" s="33" t="inlineStr">
+      <c r="F14" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2172,38 +2284,38 @@
         <f>IF(F14="Completed",1,IF(F14="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H14" s="61">
+      <c r="H14" s="64">
         <f>IF(C14="","",C14+MOD(5-WEEKDAY(C14,2),7))</f>
         <v/>
       </c>
-      <c r="I14" s="43" t="inlineStr">
-        <is>
-          <t>Edit Leave page exists with date/day-type/reason editing, weekday duration recalculation, lead-time validation, confirm modal, and rules from details page. Uses mock save until Backend Integration.</t>
+      <c r="I14" s="46" t="inlineStr">
+        <is>
+          <t>Activity Log page exists with filtering, sorting, pagination, and mock activity data.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="43" t="inlineStr">
+      <c r="A15" s="46" t="inlineStr">
         <is>
           <t>3. Employee Features</t>
         </is>
       </c>
-      <c r="B15" s="43" t="inlineStr">
-        <is>
-          <t>Cancel leave request (with required reason)</t>
-        </is>
-      </c>
-      <c r="C15" s="44" t="n">
+      <c r="B15" s="46" t="inlineStr">
+        <is>
+          <t>Edit leave request (only while still waiting for first approval)</t>
+        </is>
+      </c>
+      <c r="C15" s="47" t="n">
         <v>46225</v>
       </c>
-      <c r="D15" s="44" t="n">
+      <c r="D15" s="47" t="n">
         <v>46247</v>
       </c>
       <c r="E15" s="21">
         <f>IF(OR(C15="",D15=""),"",NETWORKDAYS(C15,D15))</f>
         <v/>
       </c>
-      <c r="F15" s="33" t="inlineStr">
+      <c r="F15" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2212,38 +2324,38 @@
         <f>IF(F15="Completed",1,IF(F15="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H15" s="61">
+      <c r="H15" s="64">
         <f>IF(C15="","",C15+MOD(5-WEEKDAY(C15,2),7))</f>
         <v/>
       </c>
-      <c r="I15" s="43" t="inlineStr">
-        <is>
-          <t>Cancel flow is present on details page with required-reason modal and success state. Uses mock action until Backend Integration.</t>
+      <c r="I15" s="46" t="inlineStr">
+        <is>
+          <t>Edit Leave page exists with date/day-type/reason editing, weekday duration recalculation, lead-time validation, confirm modal, and rules from details page. Uses mock save until Backend Integration.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="A16" s="46" t="inlineStr">
         <is>
           <t>3. Employee Features</t>
         </is>
       </c>
-      <c r="B16" s="43" t="inlineStr">
-        <is>
-          <t>Request vacation-to-sick leave conversion (upload medical certificate)</t>
-        </is>
-      </c>
-      <c r="C16" s="44" t="n">
-        <v>46226</v>
-      </c>
-      <c r="D16" s="44" t="n">
-        <v>46226</v>
+      <c r="B16" s="46" t="inlineStr">
+        <is>
+          <t>Cancel leave request (with required reason)</t>
+        </is>
+      </c>
+      <c r="C16" s="47" t="n">
+        <v>46225</v>
+      </c>
+      <c r="D16" s="47" t="n">
+        <v>46247</v>
       </c>
       <c r="E16" s="21">
         <f>IF(OR(C16="",D16=""),"",NETWORKDAYS(C16,D16))</f>
         <v/>
       </c>
-      <c r="F16" s="33" t="inlineStr">
+      <c r="F16" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2252,78 +2364,78 @@
         <f>IF(F16="Completed",1,IF(F16="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H16" s="61">
+      <c r="H16" s="64">
         <f>IF(C16="","",C16+MOD(5-WEEKDAY(C16,2),7))</f>
         <v/>
       </c>
-      <c r="I16" s="43" t="inlineStr">
+      <c r="I16" s="46" t="inlineStr">
+        <is>
+          <t>Cancel flow is present on details page with required-reason modal and success state. Uses mock action until Backend Integration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="46" t="inlineStr">
+        <is>
+          <t>3. Employee Features</t>
+        </is>
+      </c>
+      <c r="B17" s="46" t="inlineStr">
+        <is>
+          <t>Request vacation-to-sick leave conversion (upload medical certificate)</t>
+        </is>
+      </c>
+      <c r="C17" s="47" t="n">
+        <v>46226</v>
+      </c>
+      <c r="D17" s="47" t="n">
+        <v>46226</v>
+      </c>
+      <c r="E17" s="21">
+        <f>IF(OR(C17="",D17=""),"",NETWORKDAYS(C17,D17))</f>
+        <v/>
+      </c>
+      <c r="F17" s="36" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G17" s="22">
+        <f>IF(F17="Completed",1,IF(F17="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H17" s="64">
+        <f>IF(C17="","",C17+MOD(5-WEEKDAY(C17,2),7))</f>
+        <v/>
+      </c>
+      <c r="I17" s="46" t="inlineStr">
         <is>
           <t>Conversion page exists with reason + medical certificate upload, eligibility rules, confirm modal, and mock submission.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="45" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="48" t="inlineStr">
         <is>
           <t>4. Approver / Team Features</t>
         </is>
       </c>
-      <c r="B17" s="45" t="inlineStr">
+      <c r="B18" s="48" t="inlineStr">
         <is>
           <t>Approver inbox: list of leave requests waiting for action</t>
         </is>
       </c>
-      <c r="C17" s="46" t="n">
+      <c r="C18" s="49" t="n">
         <v>46226</v>
       </c>
-      <c r="D17" s="46" t="n">
-        <v>46226</v>
-      </c>
-      <c r="E17" s="24">
-        <f>IF(OR(C17="",D17=""),"",NETWORKDAYS(C17,D17))</f>
-        <v/>
-      </c>
-      <c r="F17" s="33" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="G17" s="25">
-        <f>IF(F17="Completed",1,IF(F17="In Progress",0.5,0))</f>
-        <v/>
-      </c>
-      <c r="H17" s="62">
-        <f>IF(C17="","",C17+MOD(5-WEEKDAY(C17,2),7))</f>
-        <v/>
-      </c>
-      <c r="I17" s="45" t="inlineStr">
-        <is>
-          <t>Leave Approvals page exists with pending/all tabs, search, filters, sorting, pagination, and mock queue data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="45" t="inlineStr">
-        <is>
-          <t>4. Approver / Team Features</t>
-        </is>
-      </c>
-      <c r="B18" s="45" t="inlineStr">
-        <is>
-          <t>Approve or reject leave (reject requires remarks)</t>
-        </is>
-      </c>
-      <c r="C18" s="46" t="n">
-        <v>46226</v>
-      </c>
-      <c r="D18" s="46" t="n">
+      <c r="D18" s="49" t="n">
         <v>46226</v>
       </c>
       <c r="E18" s="24">
         <f>IF(OR(C18="",D18=""),"",NETWORKDAYS(C18,D18))</f>
         <v/>
       </c>
-      <c r="F18" s="33" t="inlineStr">
+      <c r="F18" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2332,38 +2444,38 @@
         <f>IF(F18="Completed",1,IF(F18="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H18" s="62">
+      <c r="H18" s="65">
         <f>IF(C18="","",C18+MOD(5-WEEKDAY(C18,2),7))</f>
         <v/>
       </c>
-      <c r="I18" s="45" t="inlineStr">
-        <is>
-          <t>Review page supports approve/reject actions, required rejection reason, confirmation modals, and success dialogs. Uses mock actions until Backend Integration.</t>
+      <c r="I18" s="48" t="inlineStr">
+        <is>
+          <t>Leave Approvals page exists with pending/all tabs, search, filters, sorting, pagination, and mock queue data.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="45" t="inlineStr">
+      <c r="A19" s="48" t="inlineStr">
         <is>
           <t>4. Approver / Team Features</t>
         </is>
       </c>
-      <c r="B19" s="45" t="inlineStr">
-        <is>
-          <t>Show clear approval progress (who still needs to act)</t>
-        </is>
-      </c>
-      <c r="C19" s="46" t="n">
-        <v>46225</v>
-      </c>
-      <c r="D19" s="46" t="n">
-        <v>46252</v>
+      <c r="B19" s="48" t="inlineStr">
+        <is>
+          <t>Approve or reject leave (reject requires remarks)</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="n">
+        <v>46226</v>
+      </c>
+      <c r="D19" s="49" t="n">
+        <v>46226</v>
       </c>
       <c r="E19" s="24">
         <f>IF(OR(C19="",D19=""),"",NETWORKDAYS(C19,D19))</f>
         <v/>
       </c>
-      <c r="F19" s="33" t="inlineStr">
+      <c r="F19" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2372,38 +2484,38 @@
         <f>IF(F19="Completed",1,IF(F19="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H19" s="62">
+      <c r="H19" s="65">
         <f>IF(C19="","",C19+MOD(5-WEEKDAY(C19,2),7))</f>
         <v/>
       </c>
-      <c r="I19" s="45" t="inlineStr">
-        <is>
-          <t>Approval progress bars, requirement checklist, and approver status tables are built on employee details and approver review pages.</t>
+      <c r="I19" s="48" t="inlineStr">
+        <is>
+          <t>Review page supports approve/reject actions, required rejection reason, confirmation modals, and success dialogs. Uses mock actions until Backend Integration.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="45" t="inlineStr">
+      <c r="A20" s="48" t="inlineStr">
         <is>
           <t>4. Approver / Team Features</t>
         </is>
       </c>
-      <c r="B20" s="45" t="inlineStr">
-        <is>
-          <t>File leave on behalf of a team member</t>
-        </is>
-      </c>
-      <c r="C20" s="46" t="n">
-        <v>46226</v>
-      </c>
-      <c r="D20" s="46" t="n">
-        <v>46226</v>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Show clear approval progress (who still needs to act)</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n">
+        <v>46225</v>
+      </c>
+      <c r="D20" s="49" t="n">
+        <v>46252</v>
       </c>
       <c r="E20" s="24">
         <f>IF(OR(C20="",D20=""),"",NETWORKDAYS(C20,D20))</f>
         <v/>
       </c>
-      <c r="F20" s="33" t="inlineStr">
+      <c r="F20" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2412,38 +2524,38 @@
         <f>IF(F20="Completed",1,IF(F20="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H20" s="62">
+      <c r="H20" s="65">
         <f>IF(C20="","",C20+MOD(5-WEEKDAY(C20,2),7))</f>
         <v/>
       </c>
-      <c r="I20" s="45" t="inlineStr">
-        <is>
-          <t>File Leave for Member page exists with member selection, leave form, LWOP warning, attachment rules, confirm modal, and mock submit.</t>
+      <c r="I20" s="48" t="inlineStr">
+        <is>
+          <t>Approval progress bars, requirement checklist, and approver status tables are built on employee details and approver review pages.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="45" t="inlineStr">
+      <c r="A21" s="48" t="inlineStr">
         <is>
           <t>4. Approver / Team Features</t>
         </is>
       </c>
-      <c r="B21" s="45" t="inlineStr">
-        <is>
-          <t>Team leave calendar and upcoming approved leaves</t>
-        </is>
-      </c>
-      <c r="C21" s="46" t="n">
-        <v>46232</v>
-      </c>
-      <c r="D21" s="46" t="n">
-        <v>46232</v>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>File leave on behalf of a team member</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n">
+        <v>46226</v>
+      </c>
+      <c r="D21" s="49" t="n">
+        <v>46226</v>
       </c>
       <c r="E21" s="24">
         <f>IF(OR(C21="",D21=""),"",NETWORKDAYS(C21,D21))</f>
         <v/>
       </c>
-      <c r="F21" s="33" t="inlineStr">
+      <c r="F21" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2452,78 +2564,78 @@
         <f>IF(F21="Completed",1,IF(F21="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H21" s="62">
+      <c r="H21" s="65">
         <f>IF(C21="","",C21+MOD(5-WEEKDAY(C21,2),7))</f>
         <v/>
       </c>
-      <c r="I21" s="45" t="inlineStr">
+      <c r="I21" s="48" t="inlineStr">
+        <is>
+          <t>File Leave for Member page exists with member selection, leave form, LWOP warning, attachment rules, confirm modal, and mock submit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="48" t="inlineStr">
+        <is>
+          <t>4. Approver / Team Features</t>
+        </is>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Team leave calendar and upcoming approved leaves</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n">
+        <v>46232</v>
+      </c>
+      <c r="D22" s="49" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E22" s="24">
+        <f>IF(OR(C22="",D22=""),"",NETWORKDAYS(C22,D22))</f>
+        <v/>
+      </c>
+      <c r="F22" s="36" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G22" s="25">
+        <f>IF(F22="Completed",1,IF(F22="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H22" s="65">
+        <f>IF(C22="","",C22+MOD(5-WEEKDAY(C22,2),7))</f>
+        <v/>
+      </c>
+      <c r="I22" s="48" t="inlineStr">
         <is>
           <t>Team Leave Calendar page (month/week views, filters, leave chips) and Upcoming Approved Leaves page are both built with mock data.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="47" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="50" t="inlineStr">
         <is>
           <t>5. Admin Features</t>
         </is>
       </c>
-      <c r="B22" s="47" t="inlineStr">
+      <c r="B23" s="50" t="inlineStr">
         <is>
           <t>Admin view of leave requests and request details</t>
         </is>
       </c>
-      <c r="C22" s="48" t="n">
+      <c r="C23" s="51" t="n">
         <v>46232</v>
       </c>
-      <c r="D22" s="48" t="n">
-        <v>46232</v>
-      </c>
-      <c r="E22" s="27">
-        <f>IF(OR(C22="",D22=""),"",NETWORKDAYS(C22,D22))</f>
-        <v/>
-      </c>
-      <c r="F22" s="33" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="G22" s="28">
-        <f>IF(F22="Completed",1,IF(F22="In Progress",0.5,0))</f>
-        <v/>
-      </c>
-      <c r="H22" s="63">
-        <f>IF(C22="","",C22+MOD(5-WEEKDAY(C22,2),7))</f>
-        <v/>
-      </c>
-      <c r="I22" s="47" t="inlineStr">
-        <is>
-          <t>Admin Leave Requests list (pending/all tabs, filters, search, reminders) and detail/view/validate pages are all built with mock data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="47" t="inlineStr">
-        <is>
-          <t>5. Admin Features</t>
-        </is>
-      </c>
-      <c r="B23" s="47" t="inlineStr">
-        <is>
-          <t>Review vacation-to-sick leave conversion requests</t>
-        </is>
-      </c>
-      <c r="C23" s="48" t="n">
-        <v>46232</v>
-      </c>
-      <c r="D23" s="48" t="n">
+      <c r="D23" s="51" t="n">
         <v>46232</v>
       </c>
       <c r="E23" s="27">
         <f>IF(OR(C23="",D23=""),"",NETWORKDAYS(C23,D23))</f>
         <v/>
       </c>
-      <c r="F23" s="33" t="inlineStr">
+      <c r="F23" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2532,38 +2644,38 @@
         <f>IF(F23="Completed",1,IF(F23="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H23" s="63">
+      <c r="H23" s="66">
         <f>IF(C23="","",C23+MOD(5-WEEKDAY(C23,2),7))</f>
         <v/>
       </c>
-      <c r="I23" s="47" t="inlineStr">
-        <is>
-          <t>Conversion review is handled via Admin Leave Validate page; conversion state visible on request detail/view pages.</t>
+      <c r="I23" s="50" t="inlineStr">
+        <is>
+          <t>Admin Leave Requests list (pending/all tabs, filters, search, reminders) and detail/view/validate pages are all built with mock data.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="47" t="inlineStr">
+      <c r="A24" s="50" t="inlineStr">
         <is>
           <t>5. Admin Features</t>
         </is>
       </c>
-      <c r="B24" s="47" t="inlineStr">
-        <is>
-          <t>Manage leave balances and credit distribution</t>
-        </is>
-      </c>
-      <c r="C24" s="48" t="n">
+      <c r="B24" s="50" t="inlineStr">
+        <is>
+          <t>Review vacation-to-sick leave conversion requests</t>
+        </is>
+      </c>
+      <c r="C24" s="51" t="n">
         <v>46232</v>
       </c>
-      <c r="D24" s="48" t="n">
+      <c r="D24" s="51" t="n">
         <v>46232</v>
       </c>
       <c r="E24" s="27">
         <f>IF(OR(C24="",D24=""),"",NETWORKDAYS(C24,D24))</f>
         <v/>
       </c>
-      <c r="F24" s="33" t="inlineStr">
+      <c r="F24" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2572,38 +2684,38 @@
         <f>IF(F24="Completed",1,IF(F24="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H24" s="63">
+      <c r="H24" s="66">
         <f>IF(C24="","",C24+MOD(5-WEEKDAY(C24,2),7))</f>
         <v/>
       </c>
-      <c r="I24" s="47" t="inlineStr">
-        <is>
-          <t>Admin Leave Balances page with filters, adjust-credits modal, and full distribution flows (annual, newly-regularized, parental, contractual) are built with mock data.</t>
+      <c r="I24" s="50" t="inlineStr">
+        <is>
+          <t>Conversion review is handled via Admin Leave Validate page; conversion state visible on request detail/view pages.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="47" t="inlineStr">
+      <c r="A25" s="50" t="inlineStr">
         <is>
           <t>5. Admin Features</t>
         </is>
       </c>
-      <c r="B25" s="47" t="inlineStr">
-        <is>
-          <t>Administrative logs</t>
-        </is>
-      </c>
-      <c r="C25" s="48" t="n">
+      <c r="B25" s="50" t="inlineStr">
+        <is>
+          <t>Manage leave balances and credit distribution</t>
+        </is>
+      </c>
+      <c r="C25" s="51" t="n">
         <v>46232</v>
       </c>
-      <c r="D25" s="48" t="n">
+      <c r="D25" s="51" t="n">
         <v>46232</v>
       </c>
       <c r="E25" s="27">
         <f>IF(OR(C25="",D25=""),"",NETWORKDAYS(C25,D25))</f>
         <v/>
       </c>
-      <c r="F25" s="33" t="inlineStr">
+      <c r="F25" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2612,78 +2724,78 @@
         <f>IF(F25="Completed",1,IF(F25="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H25" s="63">
+      <c r="H25" s="66">
         <f>IF(C25="","",C25+MOD(5-WEEKDAY(C25,2),7))</f>
         <v/>
       </c>
-      <c r="I25" s="47" t="inlineStr">
-        <is>
-          <t>Admin Administrative Log page with search, filters, month-year picker, sorting, and pagination is built with mock data.</t>
+      <c r="I25" s="50" t="inlineStr">
+        <is>
+          <t>Admin Leave Balances page with filters, adjust-credits modal, and full distribution flows (annual, newly-regularized, parental, contractual) are built with mock data.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="47" t="inlineStr">
+      <c r="A26" s="50" t="inlineStr">
         <is>
           <t>5. Admin Features</t>
         </is>
       </c>
-      <c r="B26" s="47" t="inlineStr">
-        <is>
-          <t>Leave reports for management review</t>
-        </is>
-      </c>
-      <c r="C26" s="48" t="n">
+      <c r="B26" s="50" t="inlineStr">
+        <is>
+          <t>Administrative logs</t>
+        </is>
+      </c>
+      <c r="C26" s="51" t="n">
         <v>46232</v>
       </c>
-      <c r="D26" s="48" t="n">
+      <c r="D26" s="51" t="n">
         <v>46232</v>
       </c>
       <c r="E26" s="27">
         <f>IF(OR(C26="",D26=""),"",NETWORKDAYS(C26,D26))</f>
         <v/>
       </c>
-      <c r="F26" s="64" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="F26" s="36" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G26" s="28">
         <f>IF(F26="Completed",1,IF(F26="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H26" s="63">
+      <c r="H26" s="66">
         <f>IF(C26="","",C26+MOD(5-WEEKDAY(C26,2),7))</f>
         <v/>
       </c>
-      <c r="I26" s="47" t="inlineStr">
-        <is>
-          <t>Monthly Attendance Report page built. Leave Monetization Candidates and Employees with LWOP sub-reports are still placeholders.</t>
+      <c r="I26" s="50" t="inlineStr">
+        <is>
+          <t>Admin Administrative Log page with search, filters, month-year picker, sorting, and pagination is built with mock data.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="47" t="inlineStr">
+      <c r="A27" s="50" t="inlineStr">
         <is>
           <t>5. Admin Features</t>
         </is>
       </c>
-      <c r="B27" s="47" t="inlineStr">
-        <is>
-          <t>Support other leave types (emergency, maternity, etc.) in the screens</t>
-        </is>
-      </c>
-      <c r="C27" s="48" t="n">
-        <v>46225</v>
-      </c>
-      <c r="D27" s="48" t="n">
+      <c r="B27" s="50" t="inlineStr">
+        <is>
+          <t>Monthly Attendance Report</t>
+        </is>
+      </c>
+      <c r="C27" s="51" t="n">
+        <v>46232</v>
+      </c>
+      <c r="D27" s="51" t="n">
         <v>46232</v>
       </c>
       <c r="E27" s="27">
         <f>IF(OR(C27="",D27=""),"",NETWORKDAYS(C27,D27))</f>
         <v/>
       </c>
-      <c r="F27" s="33" t="inlineStr">
+      <c r="F27" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2692,256 +2804,276 @@
         <f>IF(F27="Completed",1,IF(F27="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H27" s="63">
+      <c r="H27" s="66">
         <f>IF(C27="","",C27+MOD(5-WEEKDAY(C27,2),7))</f>
         <v/>
       </c>
-      <c r="I27" s="47" t="inlineStr">
+      <c r="I27" s="50" t="inlineStr">
+        <is>
+          <t>Report page with month/cut-off filters, employee multi-select, group filter, calendar grid, legend, print, and download. Uses mock data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="50" t="inlineStr">
+        <is>
+          <t>5. Admin Features</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="inlineStr">
+        <is>
+          <t>Leave Monetization Candidates report</t>
+        </is>
+      </c>
+      <c r="C28" s="51" t="n">
+        <v>46233</v>
+      </c>
+      <c r="D28" s="51" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E28" s="27">
+        <f>IF(OR(C28="",D28=""),"",NETWORKDAYS(C28,D28))</f>
+        <v/>
+      </c>
+      <c r="F28" s="36" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G28" s="28">
+        <f>IF(F28="Completed",1,IF(F28="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H28" s="66">
+        <f>IF(C28="","",C28+MOD(5-WEEKDAY(C28,2),7))</f>
+        <v/>
+      </c>
+      <c r="I28" s="50" t="inlineStr">
+        <is>
+          <t>Report page with year filter, eligibility filters, sortable table, summary totals, print, and download. Uses mock data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="50" t="inlineStr">
+        <is>
+          <t>5. Admin Features</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="inlineStr">
+        <is>
+          <t>Employees with LWOP report</t>
+        </is>
+      </c>
+      <c r="C29" s="51" t="n">
+        <v>46233</v>
+      </c>
+      <c r="D29" s="51" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E29" s="27">
+        <f>IF(OR(C29="",D29=""),"",NETWORKDAYS(C29,D29))</f>
+        <v/>
+      </c>
+      <c r="F29" s="36" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G29" s="28">
+        <f>IF(F29="Completed",1,IF(F29="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H29" s="66">
+        <f>IF(C29="","",C29+MOD(5-WEEKDAY(C29,2),7))</f>
+        <v/>
+      </c>
+      <c r="I29" s="50" t="inlineStr">
+        <is>
+          <t>Report page with year and group filters, sortable LWOP summary table, print, and download. Uses mock data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="50" t="inlineStr">
+        <is>
+          <t>5. Admin Features</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="inlineStr">
+        <is>
+          <t>Support other leave types (emergency, maternity, etc.) in the screens</t>
+        </is>
+      </c>
+      <c r="C30" s="51" t="n">
+        <v>46225</v>
+      </c>
+      <c r="D30" s="51" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E30" s="27">
+        <f>IF(OR(C30="",D30=""),"",NETWORKDAYS(C30,D30))</f>
+        <v/>
+      </c>
+      <c r="F30" s="36" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G30" s="28">
+        <f>IF(F30="Completed",1,IF(F30="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H30" s="66">
+        <f>IF(C30="","",C30+MOD(5-WEEKDAY(C30,2),7))</f>
+        <v/>
+      </c>
+      <c r="I30" s="50" t="inlineStr">
         <is>
           <t>Emergency, PTB, Maternity/Paternity handled in employee/team filing and in admin screens. Monthly attendance report covers all leave categories including LWOP.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="53" t="inlineStr">
-        <is>
-          <t>6. Backend Integration (TBD)</t>
-        </is>
-      </c>
-      <c r="B28" s="53" t="inlineStr">
-        <is>
-          <t>Connect frontend to backend API (base connection and shared data types)</t>
-        </is>
-      </c>
-      <c r="C28" s="65" t="n">
-        <v>46226</v>
-      </c>
-      <c r="D28" s="65" t="n"/>
-      <c r="E28" s="30">
-        <f>IF(OR(C28="",D28=""),"",NETWORKDAYS(C28,D28))</f>
-        <v/>
-      </c>
-      <c r="F28" s="66" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G28" s="31">
-        <f>IF(F28="Completed",1,IF(F28="In Progress",0.5,0))</f>
-        <v/>
-      </c>
-      <c r="H28" s="67">
-        <f>IF(C28="","",C28+MOD(5-WEEKDAY(C28,2),7))</f>
-        <v/>
-      </c>
-      <c r="I28" s="53" t="inlineStr">
-        <is>
-          <t>Duration TBD — frontend and backend work separately. Update Start/End when schedule is known.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="53" t="inlineStr">
-        <is>
-          <t>6. Backend Integration (TBD)</t>
-        </is>
-      </c>
-      <c r="B29" s="53" t="inlineStr">
-        <is>
-          <t>Use portal cookies / session to identify the user (no separate login page)</t>
-        </is>
-      </c>
-      <c r="C29" s="65" t="n">
-        <v>46226</v>
-      </c>
-      <c r="D29" s="65" t="n"/>
-      <c r="E29" s="30">
-        <f>IF(OR(C29="",D29=""),"",NETWORKDAYS(C29,D29))</f>
-        <v/>
-      </c>
-      <c r="F29" s="66" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G29" s="31">
-        <f>IF(F29="Completed",1,IF(F29="In Progress",0.5,0))</f>
-        <v/>
-      </c>
-      <c r="H29" s="67">
-        <f>IF(C29="","",C29+MOD(5-WEEKDAY(C29,2),7))</f>
-        <v/>
-      </c>
-      <c r="I29" s="53" t="inlineStr">
-        <is>
-          <t>Duration TBD — frontend and backend work separately. Update Start/End when schedule is known. Agreed with backend: cookies/session — no login screen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="53" t="inlineStr">
-        <is>
-          <t>6. Backend Integration (TBD)</t>
-        </is>
-      </c>
-      <c r="B30" s="53" t="inlineStr">
-        <is>
-          <t>Connect employee leave screens to live API (file, history, cancel, edit)</t>
-        </is>
-      </c>
-      <c r="C30" s="65" t="n"/>
-      <c r="D30" s="65" t="n"/>
-      <c r="E30" s="30">
-        <f>IF(OR(C30="",D30=""),"",NETWORKDAYS(C30,D30))</f>
-        <v/>
-      </c>
-      <c r="F30" s="66" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G30" s="31">
-        <f>IF(F30="Completed",1,IF(F30="In Progress",0.5,0))</f>
-        <v/>
-      </c>
-      <c r="H30" s="67">
-        <f>IF(C30="","",C30+MOD(5-WEEKDAY(C30,2),7))</f>
-        <v/>
-      </c>
-      <c r="I30" s="53" t="inlineStr">
-        <is>
-          <t>Duration TBD — frontend and backend work separately. Update Start/End when schedule is known.</t>
-        </is>
-      </c>
-    </row>
     <row r="31">
-      <c r="A31" s="53" t="inlineStr">
-        <is>
-          <t>6. Backend Integration (TBD)</t>
-        </is>
-      </c>
-      <c r="B31" s="53" t="inlineStr">
-        <is>
-          <t>Connect approver / team screens to live API (inbox, approve, reject)</t>
-        </is>
-      </c>
-      <c r="C31" s="65" t="n"/>
-      <c r="D31" s="65" t="n"/>
+      <c r="A31" s="67" t="inlineStr">
+        <is>
+          <t>6. UI Polish &amp; Cleanup</t>
+        </is>
+      </c>
+      <c r="B31" s="67" t="inlineStr">
+        <is>
+          <t>Review and clean up global CSS (colors, fonts, spacing, typography)</t>
+        </is>
+      </c>
+      <c r="C31" s="68" t="n">
+        <v>46233</v>
+      </c>
+      <c r="D31" s="68" t="n">
+        <v>46242</v>
+      </c>
       <c r="E31" s="30">
         <f>IF(OR(C31="",D31=""),"",NETWORKDAYS(C31,D31))</f>
         <v/>
       </c>
-      <c r="F31" s="66" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="F31" s="69" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G31" s="31">
         <f>IF(F31="Completed",1,IF(F31="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H31" s="67">
+      <c r="H31" s="70">
         <f>IF(C31="","",C31+MOD(5-WEEKDAY(C31,2),7))</f>
         <v/>
       </c>
-      <c r="I31" s="53" t="inlineStr">
-        <is>
-          <t>Duration TBD — frontend and backend work separately. Update Start/End when schedule is known.</t>
+      <c r="I31" s="67" t="inlineStr">
+        <is>
+          <t>Currently in progress — checking index.css theme tokens, base styles, and consistency with Tailwind usage across screens.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="53" t="inlineStr">
-        <is>
-          <t>6. Backend Integration (TBD)</t>
-        </is>
-      </c>
-      <c r="B32" s="53" t="inlineStr">
-        <is>
-          <t>Connect admin screens to live API (balances, conversion, reports)</t>
-        </is>
-      </c>
-      <c r="C32" s="65" t="n"/>
-      <c r="D32" s="65" t="n"/>
+      <c r="A32" s="67" t="inlineStr">
+        <is>
+          <t>6. UI Polish &amp; Cleanup</t>
+        </is>
+      </c>
+      <c r="B32" s="67" t="inlineStr">
+        <is>
+          <t>Check and fix app shell layout (sidebar, top header, main content area)</t>
+        </is>
+      </c>
+      <c r="C32" s="68" t="n">
+        <v>46233</v>
+      </c>
+      <c r="D32" s="68" t="n">
+        <v>46242</v>
+      </c>
       <c r="E32" s="30">
         <f>IF(OR(C32="",D32=""),"",NETWORKDAYS(C32,D32))</f>
         <v/>
       </c>
-      <c r="F32" s="66" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="F32" s="69" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G32" s="31">
         <f>IF(F32="Completed",1,IF(F32="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H32" s="67">
+      <c r="H32" s="70">
         <f>IF(C32="","",C32+MOD(5-WEEKDAY(C32,2),7))</f>
         <v/>
       </c>
-      <c r="I32" s="53" t="inlineStr">
-        <is>
-          <t>Duration TBD — frontend and backend work separately. Update Start/End when schedule is known.</t>
+      <c r="I32" s="67" t="inlineStr">
+        <is>
+          <t>Currently in progress — reviewing AppLayout, collapsible sidebar, header alignment, and page padding/overflow behavior.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="53" t="inlineStr">
-        <is>
-          <t>6. Backend Integration (TBD)</t>
-        </is>
-      </c>
-      <c r="B33" s="53" t="inlineStr">
-        <is>
-          <t>Joint frontend–backend smoke check once APIs are available</t>
-        </is>
-      </c>
-      <c r="C33" s="65" t="n"/>
-      <c r="D33" s="65" t="n"/>
+      <c r="A33" s="67" t="inlineStr">
+        <is>
+          <t>6. UI Polish &amp; Cleanup</t>
+        </is>
+      </c>
+      <c r="B33" s="67" t="inlineStr">
+        <is>
+          <t>Standardize screen layouts (tables, filter bars, forms, and reports)</t>
+        </is>
+      </c>
+      <c r="C33" s="68" t="n">
+        <v>46233</v>
+      </c>
+      <c r="D33" s="68" t="n">
+        <v>46249</v>
+      </c>
       <c r="E33" s="30">
         <f>IF(OR(C33="",D33=""),"",NETWORKDAYS(C33,D33))</f>
         <v/>
       </c>
-      <c r="F33" s="66" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="F33" s="69" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G33" s="31">
         <f>IF(F33="Completed",1,IF(F33="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H33" s="67">
+      <c r="H33" s="70">
         <f>IF(C33="","",C33+MOD(5-WEEKDAY(C33,2),7))</f>
         <v/>
       </c>
-      <c r="I33" s="53" t="inlineStr">
-        <is>
-          <t>Duration TBD — frontend and backend work separately. Update Start/End when schedule is known.</t>
+      <c r="I33" s="67" t="inlineStr">
+        <is>
+          <t>Currently in progress — aligning filter control heights, table spacing, button placement, and responsive layout on list/form/report pages.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="54" t="inlineStr">
-        <is>
-          <t>7. Testing (after development)</t>
-        </is>
-      </c>
-      <c r="B34" s="54" t="inlineStr">
-        <is>
-          <t>Employee flow testing (file, edit, cancel, view history)</t>
-        </is>
-      </c>
-      <c r="C34" s="68" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D34" s="68" t="n"/>
+      <c r="A34" s="56" t="inlineStr">
+        <is>
+          <t>7. Backend Integration (TBD)</t>
+        </is>
+      </c>
+      <c r="B34" s="56" t="inlineStr">
+        <is>
+          <t>Connect frontend to backend API (base connection and shared data types)</t>
+        </is>
+      </c>
+      <c r="C34" s="71" t="n">
+        <v>46226</v>
+      </c>
+      <c r="D34" s="71" t="n"/>
       <c r="E34" s="33">
         <f>IF(OR(C34="",D34=""),"",NETWORKDAYS(C34,D34))</f>
         <v/>
       </c>
-      <c r="F34" s="66" t="inlineStr">
+      <c r="F34" s="72" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -2950,36 +3082,36 @@
         <f>IF(F34="Completed",1,IF(F34="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H34" s="69">
+      <c r="H34" s="73">
         <f>IF(C34="","",C34+MOD(5-WEEKDAY(C34,2),7))</f>
         <v/>
       </c>
-      <c r="I34" s="54" t="inlineStr">
-        <is>
-          <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
+      <c r="I34" s="56" t="inlineStr">
+        <is>
+          <t>Duration TBD — frontend and backend work separately. Update Start/End when schedule is known.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="54" t="inlineStr">
-        <is>
-          <t>7. Testing (after development)</t>
-        </is>
-      </c>
-      <c r="B35" s="54" t="inlineStr">
-        <is>
-          <t>Approver flow testing (approve, reject, team views)</t>
-        </is>
-      </c>
-      <c r="C35" s="68" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D35" s="68" t="n"/>
+      <c r="A35" s="56" t="inlineStr">
+        <is>
+          <t>7. Backend Integration (TBD)</t>
+        </is>
+      </c>
+      <c r="B35" s="56" t="inlineStr">
+        <is>
+          <t>Use portal cookies / session to identify the user (no separate login page)</t>
+        </is>
+      </c>
+      <c r="C35" s="71" t="n">
+        <v>46226</v>
+      </c>
+      <c r="D35" s="71" t="n"/>
       <c r="E35" s="33">
         <f>IF(OR(C35="",D35=""),"",NETWORKDAYS(C35,D35))</f>
         <v/>
       </c>
-      <c r="F35" s="66" t="inlineStr">
+      <c r="F35" s="72" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -2988,36 +3120,34 @@
         <f>IF(F35="Completed",1,IF(F35="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H35" s="69">
+      <c r="H35" s="73">
         <f>IF(C35="","",C35+MOD(5-WEEKDAY(C35,2),7))</f>
         <v/>
       </c>
-      <c r="I35" s="54" t="inlineStr">
-        <is>
-          <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
+      <c r="I35" s="56" t="inlineStr">
+        <is>
+          <t>Duration TBD — frontend and backend work separately. Update Start/End when schedule is known. Agreed with backend: cookies/session — no login screen.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="54" t="inlineStr">
-        <is>
-          <t>7. Testing (after development)</t>
-        </is>
-      </c>
-      <c r="B36" s="54" t="inlineStr">
-        <is>
-          <t>Admin flow testing (balances, conversion, reports)</t>
-        </is>
-      </c>
-      <c r="C36" s="68" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D36" s="68" t="n"/>
+      <c r="A36" s="56" t="inlineStr">
+        <is>
+          <t>7. Backend Integration (TBD)</t>
+        </is>
+      </c>
+      <c r="B36" s="56" t="inlineStr">
+        <is>
+          <t>Connect employee leave screens to live API (file, history, cancel, edit)</t>
+        </is>
+      </c>
+      <c r="C36" s="71" t="n"/>
+      <c r="D36" s="71" t="n"/>
       <c r="E36" s="33">
         <f>IF(OR(C36="",D36=""),"",NETWORKDAYS(C36,D36))</f>
         <v/>
       </c>
-      <c r="F36" s="66" t="inlineStr">
+      <c r="F36" s="72" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -3026,36 +3156,34 @@
         <f>IF(F36="Completed",1,IF(F36="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H36" s="69">
+      <c r="H36" s="73">
         <f>IF(C36="","",C36+MOD(5-WEEKDAY(C36,2),7))</f>
         <v/>
       </c>
-      <c r="I36" s="54" t="inlineStr">
-        <is>
-          <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
+      <c r="I36" s="56" t="inlineStr">
+        <is>
+          <t>Duration TBD — frontend and backend work separately. Update Start/End when schedule is known.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="54" t="inlineStr">
-        <is>
-          <t>7. Testing (after development)</t>
-        </is>
-      </c>
-      <c r="B37" s="54" t="inlineStr">
-        <is>
-          <t>Mobile / responsive check on common screens</t>
-        </is>
-      </c>
-      <c r="C37" s="68" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D37" s="68" t="n"/>
+      <c r="A37" s="56" t="inlineStr">
+        <is>
+          <t>7. Backend Integration (TBD)</t>
+        </is>
+      </c>
+      <c r="B37" s="56" t="inlineStr">
+        <is>
+          <t>Connect approver / team screens to live API (inbox, approve, reject)</t>
+        </is>
+      </c>
+      <c r="C37" s="71" t="n"/>
+      <c r="D37" s="71" t="n"/>
       <c r="E37" s="33">
         <f>IF(OR(C37="",D37=""),"",NETWORKDAYS(C37,D37))</f>
         <v/>
       </c>
-      <c r="F37" s="66" t="inlineStr">
+      <c r="F37" s="72" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -3064,36 +3192,34 @@
         <f>IF(F37="Completed",1,IF(F37="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H37" s="69">
+      <c r="H37" s="73">
         <f>IF(C37="","",C37+MOD(5-WEEKDAY(C37,2),7))</f>
         <v/>
       </c>
-      <c r="I37" s="54" t="inlineStr">
-        <is>
-          <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
+      <c r="I37" s="56" t="inlineStr">
+        <is>
+          <t>Duration TBD — frontend and backend work separately. Update Start/End when schedule is known.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="54" t="inlineStr">
-        <is>
-          <t>7. Testing (after development)</t>
-        </is>
-      </c>
-      <c r="B38" s="54" t="inlineStr">
-        <is>
-          <t>Fix issues found during testing</t>
-        </is>
-      </c>
-      <c r="C38" s="68" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D38" s="68" t="n"/>
+      <c r="A38" s="56" t="inlineStr">
+        <is>
+          <t>7. Backend Integration (TBD)</t>
+        </is>
+      </c>
+      <c r="B38" s="56" t="inlineStr">
+        <is>
+          <t>Connect admin screens to live API (balances, conversion, reports)</t>
+        </is>
+      </c>
+      <c r="C38" s="71" t="n"/>
+      <c r="D38" s="71" t="n"/>
       <c r="E38" s="33">
         <f>IF(OR(C38="",D38=""),"",NETWORKDAYS(C38,D38))</f>
         <v/>
       </c>
-      <c r="F38" s="66" t="inlineStr">
+      <c r="F38" s="72" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -3102,74 +3228,72 @@
         <f>IF(F38="Completed",1,IF(F38="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H38" s="69">
+      <c r="H38" s="73">
         <f>IF(C38="","",C38+MOD(5-WEEKDAY(C38,2),7))</f>
         <v/>
       </c>
-      <c r="I38" s="54" t="inlineStr">
-        <is>
-          <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
+      <c r="I38" s="56" t="inlineStr">
+        <is>
+          <t>Duration TBD — frontend and backend work separately. Update Start/End when schedule is known.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="55" t="inlineStr">
-        <is>
-          <t>8. Documentation (after development)</t>
-        </is>
-      </c>
-      <c r="B39" s="55" t="inlineStr">
-        <is>
-          <t>Finalize frontend guide for the team (FRONTEND.md)</t>
-        </is>
-      </c>
-      <c r="C39" s="70" t="n">
+      <c r="A39" s="56" t="inlineStr">
+        <is>
+          <t>7. Backend Integration (TBD)</t>
+        </is>
+      </c>
+      <c r="B39" s="56" t="inlineStr">
+        <is>
+          <t>Joint frontend–backend smoke check once APIs are available</t>
+        </is>
+      </c>
+      <c r="C39" s="71" t="n"/>
+      <c r="D39" s="71" t="n"/>
+      <c r="E39" s="33">
+        <f>IF(OR(C39="",D39=""),"",NETWORKDAYS(C39,D39))</f>
+        <v/>
+      </c>
+      <c r="F39" s="72" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G39" s="34">
+        <f>IF(F39="Completed",1,IF(F39="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H39" s="73">
+        <f>IF(C39="","",C39+MOD(5-WEEKDAY(C39,2),7))</f>
+        <v/>
+      </c>
+      <c r="I39" s="56" t="inlineStr">
+        <is>
+          <t>Duration TBD — frontend and backend work separately. Update Start/End when schedule is known.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="57" t="inlineStr">
+        <is>
+          <t>8. Testing (after development)</t>
+        </is>
+      </c>
+      <c r="B40" s="57" t="inlineStr">
+        <is>
+          <t>Employee flow testing (file, edit, cancel, view history)</t>
+        </is>
+      </c>
+      <c r="C40" s="74" t="n">
         <v>46266</v>
       </c>
-      <c r="D39" s="70" t="n"/>
-      <c r="E39" s="36">
-        <f>IF(OR(C39="",D39=""),"",NETWORKDAYS(C39,D39))</f>
-        <v/>
-      </c>
-      <c r="F39" s="66" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G39" s="37">
-        <f>IF(F39="Completed",1,IF(F39="In Progress",0.5,0))</f>
-        <v/>
-      </c>
-      <c r="H39" s="71">
-        <f>IF(C39="","",C39+MOD(5-WEEKDAY(C39,2),7))</f>
-        <v/>
-      </c>
-      <c r="I39" s="55" t="inlineStr">
-        <is>
-          <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="55" t="inlineStr">
-        <is>
-          <t>8. Documentation (after development)</t>
-        </is>
-      </c>
-      <c r="B40" s="55" t="inlineStr">
-        <is>
-          <t>Prepare short demo / walkthrough notes for stakeholders</t>
-        </is>
-      </c>
-      <c r="C40" s="70" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D40" s="70" t="n"/>
+      <c r="D40" s="74" t="n"/>
       <c r="E40" s="36">
         <f>IF(OR(C40="",D40=""),"",NETWORKDAYS(C40,D40))</f>
         <v/>
       </c>
-      <c r="F40" s="66" t="inlineStr">
+      <c r="F40" s="72" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -3178,36 +3302,36 @@
         <f>IF(F40="Completed",1,IF(F40="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H40" s="71">
+      <c r="H40" s="75">
         <f>IF(C40="","",C40+MOD(5-WEEKDAY(C40,2),7))</f>
         <v/>
       </c>
-      <c r="I40" s="55" t="inlineStr">
+      <c r="I40" s="57" t="inlineStr">
         <is>
           <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="55" t="inlineStr">
-        <is>
-          <t>8. Documentation (after development)</t>
-        </is>
-      </c>
-      <c r="B41" s="55" t="inlineStr">
-        <is>
-          <t>Handover checklist (how to run, deploy, and who owns what)</t>
-        </is>
-      </c>
-      <c r="C41" s="70" t="n">
+      <c r="A41" s="57" t="inlineStr">
+        <is>
+          <t>8. Testing (after development)</t>
+        </is>
+      </c>
+      <c r="B41" s="57" t="inlineStr">
+        <is>
+          <t>Approver flow testing (approve, reject, team views)</t>
+        </is>
+      </c>
+      <c r="C41" s="74" t="n">
         <v>46266</v>
       </c>
-      <c r="D41" s="70" t="n"/>
+      <c r="D41" s="74" t="n"/>
       <c r="E41" s="36">
         <f>IF(OR(C41="",D41=""),"",NETWORKDAYS(C41,D41))</f>
         <v/>
       </c>
-      <c r="F41" s="66" t="inlineStr">
+      <c r="F41" s="72" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -3216,29 +3340,257 @@
         <f>IF(F41="Completed",1,IF(F41="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H41" s="71">
+      <c r="H41" s="75">
         <f>IF(C41="","",C41+MOD(5-WEEKDAY(C41,2),7))</f>
         <v/>
       </c>
-      <c r="I41" s="55" t="inlineStr">
+      <c r="I41" s="57" t="inlineStr">
         <is>
           <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="57" t="inlineStr">
+        <is>
+          <t>8. Testing (after development)</t>
+        </is>
+      </c>
+      <c r="B42" s="57" t="inlineStr">
+        <is>
+          <t>Admin flow testing (balances, conversion, reports)</t>
+        </is>
+      </c>
+      <c r="C42" s="74" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D42" s="74" t="n"/>
+      <c r="E42" s="36">
+        <f>IF(OR(C42="",D42=""),"",NETWORKDAYS(C42,D42))</f>
+        <v/>
+      </c>
+      <c r="F42" s="72" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G42" s="37">
+        <f>IF(F42="Completed",1,IF(F42="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H42" s="75">
+        <f>IF(C42="","",C42+MOD(5-WEEKDAY(C42,2),7))</f>
+        <v/>
+      </c>
+      <c r="I42" s="57" t="inlineStr">
+        <is>
+          <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
+        </is>
+      </c>
+    </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="57" t="inlineStr">
+        <is>
+          <t>8. Testing (after development)</t>
+        </is>
+      </c>
+      <c r="B43" s="57" t="inlineStr">
+        <is>
+          <t>Mobile / responsive check on common screens</t>
+        </is>
+      </c>
+      <c r="C43" s="74" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D43" s="74" t="n"/>
+      <c r="E43" s="36">
+        <f>IF(OR(C43="",D43=""),"",NETWORKDAYS(C43,D43))</f>
+        <v/>
+      </c>
+      <c r="F43" s="72" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G43" s="37">
+        <f>IF(F43="Completed",1,IF(F43="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H43" s="75">
+        <f>IF(C43="","",C43+MOD(5-WEEKDAY(C43,2),7))</f>
+        <v/>
+      </c>
+      <c r="I43" s="57" t="inlineStr">
+        <is>
+          <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="57" t="inlineStr">
+        <is>
+          <t>8. Testing (after development)</t>
+        </is>
+      </c>
+      <c r="B44" s="57" t="inlineStr">
+        <is>
+          <t>Fix issues found during testing</t>
+        </is>
+      </c>
+      <c r="C44" s="74" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D44" s="74" t="n"/>
+      <c r="E44" s="36">
+        <f>IF(OR(C44="",D44=""),"",NETWORKDAYS(C44,D44))</f>
+        <v/>
+      </c>
+      <c r="F44" s="72" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G44" s="37">
+        <f>IF(F44="Completed",1,IF(F44="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H44" s="75">
+        <f>IF(C44="","",C44+MOD(5-WEEKDAY(C44,2),7))</f>
+        <v/>
+      </c>
+      <c r="I44" s="57" t="inlineStr">
+        <is>
+          <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="58" t="inlineStr">
+        <is>
+          <t>9. Documentation (after development)</t>
+        </is>
+      </c>
+      <c r="B45" s="58" t="inlineStr">
+        <is>
+          <t>Finalize frontend guide for the team (FRONTEND.md)</t>
+        </is>
+      </c>
+      <c r="C45" s="76" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D45" s="76" t="n"/>
+      <c r="E45" s="39">
+        <f>IF(OR(C45="",D45=""),"",NETWORKDAYS(C45,D45))</f>
+        <v/>
+      </c>
+      <c r="F45" s="72" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G45" s="40">
+        <f>IF(F45="Completed",1,IF(F45="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H45" s="77">
+        <f>IF(C45="","",C45+MOD(5-WEEKDAY(C45,2),7))</f>
+        <v/>
+      </c>
+      <c r="I45" s="58" t="inlineStr">
+        <is>
+          <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="58" t="inlineStr">
+        <is>
+          <t>9. Documentation (after development)</t>
+        </is>
+      </c>
+      <c r="B46" s="58" t="inlineStr">
+        <is>
+          <t>Prepare short demo / walkthrough notes for stakeholders</t>
+        </is>
+      </c>
+      <c r="C46" s="76" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D46" s="76" t="n"/>
+      <c r="E46" s="39">
+        <f>IF(OR(C46="",D46=""),"",NETWORKDAYS(C46,D46))</f>
+        <v/>
+      </c>
+      <c r="F46" s="72" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G46" s="40">
+        <f>IF(F46="Completed",1,IF(F46="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H46" s="77">
+        <f>IF(C46="","",C46+MOD(5-WEEKDAY(C46,2),7))</f>
+        <v/>
+      </c>
+      <c r="I46" s="58" t="inlineStr">
+        <is>
+          <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="58" t="inlineStr">
+        <is>
+          <t>9. Documentation (after development)</t>
+        </is>
+      </c>
+      <c r="B47" s="58" t="inlineStr">
+        <is>
+          <t>Handover checklist (how to run, deploy, and who owns what)</t>
+        </is>
+      </c>
+      <c r="C47" s="76" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D47" s="76" t="n"/>
+      <c r="E47" s="39">
+        <f>IF(OR(C47="",D47=""),"",NETWORKDAYS(C47,D47))</f>
+        <v/>
+      </c>
+      <c r="F47" s="72" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G47" s="40">
+        <f>IF(F47="Completed",1,IF(F47="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H47" s="77">
+        <f>IF(C47="","",C47+MOD(5-WEEKDAY(C47,2),7))</f>
+        <v/>
+      </c>
+      <c r="I47" s="58" t="inlineStr">
+        <is>
+          <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Commitment: frontend DEVELOPMENT finished by end of August (weekdays = NETWORKDAYS). Backend Integration has TBD end dates (teams work separately — fill dates when known). Testing and Documentation start after development (from Sep 2026); end dates TBD. No login page — portal cookies/session with backend.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I41"/>
+  <autoFilter ref="A1:I47"/>
   <mergeCells count="1">
-    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A49:I49"/>
   </mergeCells>
-  <conditionalFormatting sqref="G2:G41">
+  <conditionalFormatting sqref="G2:G47">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -3251,7 +3603,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="F2:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Not Started,In Progress,Completed,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3279,168 +3631,168 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="72" t="inlineStr"/>
+      <c r="A2" s="78" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="73" t="inlineStr">
+      <c r="A3" s="79" t="inlineStr">
         <is>
           <t>August commitment</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="72" t="inlineStr">
+      <c r="A4" s="78" t="inlineStr">
         <is>
           <t>Only frontend DEVELOPMENT is committed to finish by end of August.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="72" t="inlineStr">
+      <c r="A5" s="78" t="inlineStr">
         <is>
           <t>Testing and documentation come AFTER development (start ~1 Sep; end dates TBD).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="72" t="inlineStr">
+      <c r="A6" s="78" t="inlineStr">
         <is>
           <t>Backend Integration is listed with TBD dates — teams work separately for now.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="72" t="inlineStr"/>
+      <c r="A7" s="78" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="73" t="inlineStr">
+      <c r="A8" s="79" t="inlineStr">
         <is>
           <t>For leaders / managers</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="72" t="inlineStr">
-        <is>
-          <t>1. Dashboard — overall % and section progress (also see Development progress for sections 1–5).</t>
+      <c r="A9" s="78" t="inlineStr">
+        <is>
+          <t>1. Dashboard — overall % and section progress (also see Development progress for sections 1–6).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="72" t="inlineStr">
+      <c r="A10" s="78" t="inlineStr">
         <is>
           <t>2. Tentative Schedule — development phases through August; backend/testing/docs called out as TBD/after.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="72" t="inlineStr">
+      <c r="A11" s="78" t="inlineStr">
         <is>
           <t>3. Progress Tracker — update Status here.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="72" t="inlineStr"/>
+      <c r="A12" s="78" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="73" t="inlineStr">
+      <c r="A13" s="79" t="inlineStr">
         <is>
           <t>For the development team</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="72" t="inlineStr">
+      <c r="A14" s="78" t="inlineStr">
         <is>
           <t>1. Change Status on Progress Tracker (dropdown).</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="72" t="inlineStr">
+      <c r="A15" s="78" t="inlineStr">
         <is>
           <t>2. For Backend Integration / Testing / Documentation: fill Start and End dates when known.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="72" t="inlineStr">
+      <c r="A16" s="78" t="inlineStr">
         <is>
           <t>3. Keyword for Cursor: Update the leader tracker from the code</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="72" t="inlineStr"/>
+      <c r="A17" s="78" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="73" t="inlineStr">
+      <c r="A18" s="79" t="inlineStr">
         <is>
           <t>Workdays</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="72" t="inlineStr">
+      <c r="A19" s="78" t="inlineStr">
         <is>
           <t>Days (weekdays) uses NETWORKDAYS when both Start and End are filled (Mon–Fri only).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="72" t="inlineStr"/>
+      <c r="A20" s="78" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="73" t="inlineStr">
+      <c r="A21" s="79" t="inlineStr">
         <is>
           <t>Authentication</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="72" t="inlineStr">
+      <c r="A22" s="78" t="inlineStr">
         <is>
           <t>No login page. User identity via portal cookies/session with the backend partner.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="72" t="inlineStr"/>
+      <c r="A23" s="78" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="73" t="inlineStr">
+      <c r="A24" s="79" t="inlineStr">
         <is>
           <t>Status meanings</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="72" t="inlineStr">
+      <c r="A25" s="78" t="inlineStr">
         <is>
           <t>Completed / In Progress / Not Started / Blocked</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="72" t="inlineStr">
+      <c r="A26" s="78" t="inlineStr">
         <is>
           <t>Scoring: Completed = 100%, In Progress = 50%, else 0%.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="72" t="inlineStr"/>
+      <c r="A27" s="78" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="73" t="inlineStr">
+      <c r="A28" s="79" t="inlineStr">
         <is>
           <t>Related files</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="72" t="inlineStr">
+      <c r="A29" s="78" t="inlineStr">
         <is>
           <t>docs/FRONTEND.md</t>
         </is>

--- a/docs/FRONTEND_LEADER_TRACKER.xlsx
+++ b/docs/FRONTEND_LEADER_TRACKER.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tentative Schedule" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Progress Tracker" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="How to use" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tentative Schedule" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progress Tracker" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Progress Tracker'!$A$1:$I$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Progress Tracker'!$A$1:$I$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -141,17 +141,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E2D5F1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EAD1DC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -218,7 +218,7 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -230,7 +230,7 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -267,18 +267,18 @@
     <xf numFmtId="9" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -313,8 +313,8 @@
     <xf numFmtId="165" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -339,22 +339,22 @@
     <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -761,14 +761,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Backend Integration is listed separately — schedule depends on the backend partner. No separate login page (portal cookies/session). Days = weekdays only when both dates are set.</t>
+          <t>Backend Integration is underway (employee + key approver screens on live API). Production auth is portal cookies/session (dev-only employee ID entry for local testing). Days = weekdays only when both dates are set.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Last aligned to codebase: 2026-07-30 — all screens built with mock data; currently polishing CSS and layouts (section 6); cookie/session and live API not wired yet.</t>
+          <t>Last aligned to codebase: 2026-08-13 — live API wired for auth + employee + key approver flows; admin still mock; CODEBASE REVIEW AND CLEANUP STILL IN PROGRESS (section 6).</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
         <v>46233</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="D9" s="18">
         <f>NETWORKDAYS(B9,C9)</f>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E9" s="52" t="inlineStr">
         <is>
-          <t>CSS review, layout checks, and consistent spacing across screens.</t>
+          <t>CSS/layout review STILL IN PROGRESS; shared leave components and empty states landed.</t>
         </is>
       </c>
       <c r="F9" s="53">
@@ -1411,12 +1411,12 @@
     <row r="15">
       <c r="A15" s="56" t="inlineStr">
         <is>
-          <t>Backend integration (parallel / TBD)</t>
+          <t>Backend integration (in progress)</t>
         </is>
       </c>
       <c r="B15" s="56" t="inlineStr">
         <is>
-          <t>Ongoing with backend partner — no fixed day count yet. Update when APIs and cookie/session are ready.</t>
+          <t>Employee + key approver APIs wired (as of 2026-08-13). Admin APIs and remaining team screens still TBD.</t>
         </is>
       </c>
     </row>
@@ -1495,11 +1495,11 @@
     <row r="23">
       <c r="A23" s="59" t="inlineStr">
         <is>
-          <t>Reusable UI + employee screens underway</t>
+          <t>Admin screens usable (UI) — done early</t>
         </is>
       </c>
       <c r="B23" s="60" t="n">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="C23" s="60">
         <f>B23+MOD(5-WEEKDAY(B23,2),7)</f>
@@ -1507,18 +1507,18 @@
       </c>
       <c r="D23" s="59" t="inlineStr">
         <is>
-          <t>2–3</t>
+          <t>5. Admin Features</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="59" t="inlineStr">
         <is>
-          <t>Employee filing &amp; history usable (UI)</t>
+          <t>UI polish &amp; layout cleanup underway</t>
         </is>
       </c>
       <c r="B24" s="60" t="n">
-        <v>46247</v>
+        <v>46233</v>
       </c>
       <c r="C24" s="60">
         <f>B24+MOD(5-WEEKDAY(B24,2),7)</f>
@@ -1526,18 +1526,18 @@
       </c>
       <c r="D24" s="59" t="inlineStr">
         <is>
-          <t>3. Employee Features</t>
+          <t>6. UI Polish &amp; Cleanup</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="59" t="inlineStr">
         <is>
-          <t>Approver approve/reject usable (UI)</t>
+          <t>Notifications + error pages</t>
         </is>
       </c>
       <c r="B25" s="60" t="n">
-        <v>46252</v>
+        <v>46234</v>
       </c>
       <c r="C25" s="60">
         <f>B25+MOD(5-WEEKDAY(B25,2),7)</f>
@@ -1545,18 +1545,18 @@
       </c>
       <c r="D25" s="59" t="inlineStr">
         <is>
-          <t>4. Approver / Team</t>
+          <t>2. Core App Shell</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="59" t="inlineStr">
         <is>
-          <t>Admin screens usable (UI) — done early</t>
+          <t>Employee + approver live API wiring started</t>
         </is>
       </c>
       <c r="B26" s="60" t="n">
-        <v>46233</v>
+        <v>46245</v>
       </c>
       <c r="C26" s="60">
         <f>B26+MOD(5-WEEKDAY(B26,2),7)</f>
@@ -1564,18 +1564,18 @@
       </c>
       <c r="D26" s="59" t="inlineStr">
         <is>
-          <t>5. Admin Features</t>
+          <t>7. Backend Integration</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="59" t="inlineStr">
         <is>
-          <t>Admin screens target (original plan)</t>
+          <t>Codebase review &amp; cleanup still in progress</t>
         </is>
       </c>
       <c r="B27" s="60" t="n">
-        <v>46262</v>
+        <v>46247</v>
       </c>
       <c r="C27" s="60">
         <f>B27+MOD(5-WEEKDAY(B27,2),7)</f>
@@ -1583,18 +1583,18 @@
       </c>
       <c r="D27" s="59" t="inlineStr">
         <is>
-          <t>5. Admin Features</t>
+          <t>6. UI Polish &amp; Cleanup</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="59" t="inlineStr">
         <is>
-          <t>UI polish &amp; layout cleanup underway</t>
+          <t>Live auth + employee/approver APIs in progress</t>
         </is>
       </c>
       <c r="B28" s="60" t="n">
-        <v>46233</v>
+        <v>46247</v>
       </c>
       <c r="C28" s="60">
         <f>B28+MOD(5-WEEKDAY(B28,2),7)</f>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="D28" s="59" t="inlineStr">
         <is>
-          <t>6. UI Polish &amp; Cleanup</t>
+          <t>7. Backend Integration</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D29" s="59" t="inlineStr">
         <is>
-          <t>Sections 1–6</t>
+          <t>Sections 1–7</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B36" s="59" t="inlineStr">
         <is>
-          <t>CSS and layout cleanup in progress across screens</t>
+          <t>CSS/layout cleanup in progress; shared leave detail layout improvements</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B37" s="59" t="inlineStr">
         <is>
-          <t>Layout polish wrapping up; ready for backend hookup when APIs are available</t>
+          <t>Codebase review still in progress; live auth + employee/approver APIs wired</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B38" s="59" t="inlineStr">
         <is>
-          <t>Approver UI in place; admin screens underway</t>
+          <t>Continue UI polish + finish remaining API wiring (team calendar, admin)</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="B39" s="59" t="inlineStr">
         <is>
-          <t>Admin UI in progress / wrapping up</t>
+          <t>Wrap remaining polish and admin API work before Aug commitment</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1896,7 +1896,11 @@
         <f>IF(C4="","",C4+MOD(5-WEEKDAY(C4,2),7))</f>
         <v/>
       </c>
-      <c r="I4" s="44" t="inlineStr"/>
+      <c r="I4" s="44" t="inlineStr">
+        <is>
+          <t>Routes include RequireAuth / RequireCapability gates and error preview paths.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="52" t="inlineStr">
@@ -1949,7 +1953,7 @@
         <v>46224</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>46225</v>
+        <v>46247</v>
       </c>
       <c r="E6" s="18">
         <f>IF(OR(C6="",D6=""),"",NETWORKDAYS(C6,D6))</f>
@@ -1970,7 +1974,7 @@
       </c>
       <c r="I6" s="52" t="inlineStr">
         <is>
-          <t>Role-based sidebar works. Dev-only role preview remains until portal cookies/session are wired.</t>
+          <t>Sidebar + RequireCapability use live roles from /api/me (approver/admin). Dev persona switcher removed as auth is wired.</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1993,7 @@
         <v>46225</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>46233</v>
+        <v>46247</v>
       </c>
       <c r="E7" s="18">
         <f>IF(OR(C7="",D7=""),"",NETWORKDAYS(C7,D7))</f>
@@ -2010,7 +2014,7 @@
       </c>
       <c r="I7" s="52" t="inlineStr">
         <is>
-          <t>Built: StatusBadge, FilterSelect, Pagination, Button, Modal, ConfirmReasonModal, AttachmentPreviewModal, SuccessDialog, Skeleton, form fields, MonthYearPickerField, YearPickerField, EmployeeMultiSelect, tableStyles, admin-specific components.</t>
+          <t>Built: StatusBadge, FilterSelect, Pagination, Button, Modal, ConfirmReasonModal, AttachmentPreviewModal, SuccessDialog, Skeleton, EmptyState, TableEmptyRow, SortableHeader, ListTabButton, PageBackLink, NotificationPanel, form fields, shared leave panels, tableStyles/tableLayout, admin components.</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2054,7 @@
       </c>
       <c r="I8" s="52" t="inlineStr">
         <is>
-          <t>Sidebar collapses to icon-only mode with flyout submenus, tooltips, and localStorage preference. Top header toggle wired in AppLayout.</t>
+          <t>Collapsible sidebar with flyouts, localStorage preference, and responsive/mobile behavior (useMediaQuery).</t>
         </is>
       </c>
     </row>
@@ -2062,14 +2066,14 @@
       </c>
       <c r="B9" s="52" t="inlineStr">
         <is>
-          <t>Replace temporary placeholder pages with real screens</t>
+          <t>In-app notifications panel (header bell)</t>
         </is>
       </c>
       <c r="C9" s="53" t="n">
-        <v>46225</v>
+        <v>46234</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E9" s="18">
         <f>IF(OR(C9="",D9=""),"",NETWORKDAYS(C9,D9))</f>
@@ -2090,87 +2094,87 @@
       </c>
       <c r="I9" s="52" t="inlineStr">
         <is>
-          <t>All employee, approver/team, and admin routes now have real page components. PagePlaceholder is no longer used in routing.</t>
+          <t>NotificationPanel in TopHeader (unread filter, mark read). Still uses mock notifications until a notifications API is available.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="46" t="inlineStr">
-        <is>
-          <t>3. Employee Features</t>
-        </is>
-      </c>
-      <c r="B10" s="46" t="inlineStr">
-        <is>
-          <t>Employee dashboard: leave balances and recent requests</t>
-        </is>
-      </c>
-      <c r="C10" s="47" t="n">
+      <c r="A10" s="52" t="inlineStr">
+        <is>
+          <t>2. Core App Shell</t>
+        </is>
+      </c>
+      <c r="B10" s="52" t="inlineStr">
+        <is>
+          <t>Error and system feedback pages (401, 403, 404, 409, 500, 503, offline)</t>
+        </is>
+      </c>
+      <c r="C10" s="53" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D10" s="53" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E10" s="18">
+        <f>IF(OR(C10="",D10=""),"",NETWORKDAYS(C10,D10))</f>
+        <v/>
+      </c>
+      <c r="F10" s="36" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G10" s="19">
+        <f>IF(F10="Completed",1,IF(F10="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H10" s="63">
+        <f>IF(C10="","",C10+MOD(5-WEEKDAY(C10,2),7))</f>
+        <v/>
+      </c>
+      <c r="I10" s="52" t="inlineStr">
+        <is>
+          <t>Shared ErrorPage layout + dedicated routes. Catch-all invalid URLs show NotFound without redirecting away from the URL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="52" t="inlineStr">
+        <is>
+          <t>2. Core App Shell</t>
+        </is>
+      </c>
+      <c r="B11" s="52" t="inlineStr">
+        <is>
+          <t>Replace temporary placeholder pages with real screens</t>
+        </is>
+      </c>
+      <c r="C11" s="53" t="n">
         <v>46225</v>
       </c>
-      <c r="D10" s="47" t="n">
-        <v>46225</v>
-      </c>
-      <c r="E10" s="21">
-        <f>IF(OR(C10="",D10=""),"",NETWORKDAYS(C10,D10))</f>
-        <v/>
-      </c>
-      <c r="F10" s="36" t="inlineStr">
+      <c r="D11" s="53" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E11" s="18">
+        <f>IF(OR(C11="",D11=""),"",NETWORKDAYS(C11,D11))</f>
+        <v/>
+      </c>
+      <c r="F11" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="G10" s="22">
-        <f>IF(F10="Completed",1,IF(F10="In Progress",0.5,0))</f>
-        <v/>
-      </c>
-      <c r="H10" s="64">
-        <f>IF(C10="","",C10+MOD(5-WEEKDAY(C10,2),7))</f>
-        <v/>
-      </c>
-      <c r="I10" s="46" t="inlineStr">
-        <is>
-          <t>UI complete (balances, reserved credits, filters, pagination). Uses mock data until Backend Integration.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="46" t="inlineStr">
-        <is>
-          <t>3. Employee Features</t>
-        </is>
-      </c>
-      <c r="B11" s="46" t="inlineStr">
-        <is>
-          <t>File leave request (dates, leave type, reason, attachment)</t>
-        </is>
-      </c>
-      <c r="C11" s="47" t="n">
-        <v>46226</v>
-      </c>
-      <c r="D11" s="47" t="n">
-        <v>46226</v>
-      </c>
-      <c r="E11" s="21">
-        <f>IF(OR(C11="",D11=""),"",NETWORKDAYS(C11,D11))</f>
-        <v/>
-      </c>
-      <c r="F11" s="36" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="G11" s="22">
+      <c r="G11" s="19">
         <f>IF(F11="Completed",1,IF(F11="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H11" s="64">
+      <c r="H11" s="63">
         <f>IF(C11="","",C11+MOD(5-WEEKDAY(C11,2),7))</f>
         <v/>
       </c>
-      <c r="I11" s="46" t="inlineStr">
-        <is>
-          <t>Apply Leave page is built with employee info, leave type/day type, date range, reason, attachment rules, duration preview, confirm modal, and success dialog. Uses mock submit until Backend Integration.</t>
+      <c r="I11" s="52" t="inlineStr">
+        <is>
+          <t>All feature routes use real pages. PagePlaceholder and unused icons removed. Empty lists use EmptyState / TableEmptyRow.</t>
         </is>
       </c>
     </row>
@@ -2182,14 +2186,14 @@
       </c>
       <c r="B12" s="46" t="inlineStr">
         <is>
-          <t>Show unpaid leave (LWOP) warning when credits are not enough</t>
+          <t>Employee dashboard: leave balances and recent requests</t>
         </is>
       </c>
       <c r="C12" s="47" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="D12" s="47" t="n">
-        <v>46226</v>
+        <v>46247</v>
       </c>
       <c r="E12" s="21">
         <f>IF(OR(C12="",D12=""),"",NETWORKDAYS(C12,D12))</f>
@@ -2210,7 +2214,7 @@
       </c>
       <c r="I12" s="46" t="inlineStr">
         <is>
-          <t>LWOP / remaining-balance warning is shown in filing forms using mock remaining-day logic.</t>
+          <t>UI complete; now loads live balances and leave list via useMyBalances / useMyLeaves (SWR).</t>
         </is>
       </c>
     </row>
@@ -2222,14 +2226,14 @@
       </c>
       <c r="B13" s="46" t="inlineStr">
         <is>
-          <t>Leave request details: status, approvals needed, and activity history</t>
+          <t>File leave request (dates, leave type, reason, attachment)</t>
         </is>
       </c>
       <c r="C13" s="47" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="D13" s="47" t="n">
-        <v>46225</v>
+        <v>46247</v>
       </c>
       <c r="E13" s="21">
         <f>IF(OR(C13="",D13=""),"",NETWORKDAYS(C13,D13))</f>
@@ -2250,7 +2254,7 @@
       </c>
       <c r="I13" s="46" t="inlineStr">
         <is>
-          <t>UI complete: leave info, approval progress/requirements, approver list, attachments, conversion view. Mock data; activity timeline not a separate log yet.</t>
+          <t>Apply Leave submits via createLeave API; holiday dates from live holidays hook. Multi-file attachments supported.</t>
         </is>
       </c>
     </row>
@@ -2262,14 +2266,14 @@
       </c>
       <c r="B14" s="46" t="inlineStr">
         <is>
-          <t>Activity log / leave history with filters</t>
+          <t>Show unpaid leave (LWOP) warning when credits are not enough</t>
         </is>
       </c>
       <c r="C14" s="47" t="n">
         <v>46226</v>
       </c>
       <c r="D14" s="47" t="n">
-        <v>46226</v>
+        <v>46247</v>
       </c>
       <c r="E14" s="21">
         <f>IF(OR(C14="",D14=""),"",NETWORKDAYS(C14,D14))</f>
@@ -2290,7 +2294,7 @@
       </c>
       <c r="I14" s="46" t="inlineStr">
         <is>
-          <t>Activity Log page exists with filtering, sorting, pagination, and mock activity data.</t>
+          <t>LWOP / remaining-balance warning shown in filing forms using live balance data where available.</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2306,7 @@
       </c>
       <c r="B15" s="46" t="inlineStr">
         <is>
-          <t>Edit leave request (only while still waiting for first approval)</t>
+          <t>Leave request details: status, approvals needed, and activity history</t>
         </is>
       </c>
       <c r="C15" s="47" t="n">
@@ -2330,7 +2334,7 @@
       </c>
       <c r="I15" s="46" t="inlineStr">
         <is>
-          <t>Edit Leave page exists with date/day-type/reason editing, weekday duration recalculation, lead-time validation, confirm modal, and rules from details page. Uses mock save until Backend Integration.</t>
+          <t>Details page uses live useLeaveDetail + Approval Details table. Cancel calls live cancelLeave API.</t>
         </is>
       </c>
     </row>
@@ -2342,11 +2346,11 @@
       </c>
       <c r="B16" s="46" t="inlineStr">
         <is>
-          <t>Cancel leave request (with required reason)</t>
+          <t>Activity log / leave history with filters</t>
         </is>
       </c>
       <c r="C16" s="47" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="D16" s="47" t="n">
         <v>46247</v>
@@ -2370,7 +2374,7 @@
       </c>
       <c r="I16" s="46" t="inlineStr">
         <is>
-          <t>Cancel flow is present on details page with required-reason modal and success state. Uses mock action until Backend Integration.</t>
+          <t>Activity Log page wired to live useActivities API with filters, sorting, and pagination.</t>
         </is>
       </c>
     </row>
@@ -2382,14 +2386,14 @@
       </c>
       <c r="B17" s="46" t="inlineStr">
         <is>
-          <t>Request vacation-to-sick leave conversion (upload medical certificate)</t>
+          <t>Edit leave request (only while still waiting for first approval)</t>
         </is>
       </c>
       <c r="C17" s="47" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="D17" s="47" t="n">
-        <v>46226</v>
+        <v>46247</v>
       </c>
       <c r="E17" s="21">
         <f>IF(OR(C17="",D17=""),"",NETWORKDAYS(C17,D17))</f>
@@ -2410,87 +2414,87 @@
       </c>
       <c r="I17" s="46" t="inlineStr">
         <is>
-          <t>Conversion page exists with reason + medical certificate upload, eligibility rules, confirm modal, and mock submission.</t>
+          <t>Edit Leave loads live detail and saves via updateLeave API; holiday dates from live hook.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="48" t="inlineStr">
-        <is>
-          <t>4. Approver / Team Features</t>
-        </is>
-      </c>
-      <c r="B18" s="48" t="inlineStr">
-        <is>
-          <t>Approver inbox: list of leave requests waiting for action</t>
-        </is>
-      </c>
-      <c r="C18" s="49" t="n">
+      <c r="A18" s="46" t="inlineStr">
+        <is>
+          <t>3. Employee Features</t>
+        </is>
+      </c>
+      <c r="B18" s="46" t="inlineStr">
+        <is>
+          <t>Cancel leave request (with required reason)</t>
+        </is>
+      </c>
+      <c r="C18" s="47" t="n">
+        <v>46225</v>
+      </c>
+      <c r="D18" s="47" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E18" s="21">
+        <f>IF(OR(C18="",D18=""),"",NETWORKDAYS(C18,D18))</f>
+        <v/>
+      </c>
+      <c r="F18" s="36" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G18" s="22">
+        <f>IF(F18="Completed",1,IF(F18="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H18" s="64">
+        <f>IF(C18="","",C18+MOD(5-WEEKDAY(C18,2),7))</f>
+        <v/>
+      </c>
+      <c r="I18" s="46" t="inlineStr">
+        <is>
+          <t>Cancel flow on details page with required reason; live cancelLeave + cache revalidation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="46" t="inlineStr">
+        <is>
+          <t>3. Employee Features</t>
+        </is>
+      </c>
+      <c r="B19" s="46" t="inlineStr">
+        <is>
+          <t>Request vacation-to-sick leave conversion (upload medical certificate)</t>
+        </is>
+      </c>
+      <c r="C19" s="47" t="n">
         <v>46226</v>
       </c>
-      <c r="D18" s="49" t="n">
-        <v>46226</v>
-      </c>
-      <c r="E18" s="24">
-        <f>IF(OR(C18="",D18=""),"",NETWORKDAYS(C18,D18))</f>
-        <v/>
-      </c>
-      <c r="F18" s="36" t="inlineStr">
+      <c r="D19" s="47" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E19" s="21">
+        <f>IF(OR(C19="",D19=""),"",NETWORKDAYS(C19,D19))</f>
+        <v/>
+      </c>
+      <c r="F19" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="G18" s="25">
-        <f>IF(F18="Completed",1,IF(F18="In Progress",0.5,0))</f>
-        <v/>
-      </c>
-      <c r="H18" s="65">
-        <f>IF(C18="","",C18+MOD(5-WEEKDAY(C18,2),7))</f>
-        <v/>
-      </c>
-      <c r="I18" s="48" t="inlineStr">
-        <is>
-          <t>Leave Approvals page exists with pending/all tabs, search, filters, sorting, pagination, and mock queue data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="48" t="inlineStr">
-        <is>
-          <t>4. Approver / Team Features</t>
-        </is>
-      </c>
-      <c r="B19" s="48" t="inlineStr">
-        <is>
-          <t>Approve or reject leave (reject requires remarks)</t>
-        </is>
-      </c>
-      <c r="C19" s="49" t="n">
-        <v>46226</v>
-      </c>
-      <c r="D19" s="49" t="n">
-        <v>46226</v>
-      </c>
-      <c r="E19" s="24">
-        <f>IF(OR(C19="",D19=""),"",NETWORKDAYS(C19,D19))</f>
-        <v/>
-      </c>
-      <c r="F19" s="36" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="G19" s="25">
+      <c r="G19" s="22">
         <f>IF(F19="Completed",1,IF(F19="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H19" s="65">
+      <c r="H19" s="64">
         <f>IF(C19="","",C19+MOD(5-WEEKDAY(C19,2),7))</f>
         <v/>
       </c>
-      <c r="I19" s="48" t="inlineStr">
-        <is>
-          <t>Review page supports approve/reject actions, required rejection reason, confirmation modals, and success dialogs. Uses mock actions until Backend Integration.</t>
+      <c r="I19" s="46" t="inlineStr">
+        <is>
+          <t>Conversion page uses live leave detail and requestConversion API (multipart med cert).</t>
         </is>
       </c>
     </row>
@@ -2502,14 +2506,14 @@
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Show clear approval progress (who still needs to act)</t>
+          <t>Approver inbox: list of leave requests waiting for action</t>
         </is>
       </c>
       <c r="C20" s="49" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="D20" s="49" t="n">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="E20" s="24">
         <f>IF(OR(C20="",D20=""),"",NETWORKDAYS(C20,D20))</f>
@@ -2530,7 +2534,7 @@
       </c>
       <c r="I20" s="48" t="inlineStr">
         <is>
-          <t>Approval progress bars, requirement checklist, and approver status tables are built on employee details and approver review pages.</t>
+          <t>Leave Approvals inbox uses live usePendingApprovals / useApprovals (pending + all tabs).</t>
         </is>
       </c>
     </row>
@@ -2542,14 +2546,14 @@
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>File leave on behalf of a team member</t>
+          <t>Approve or reject leave (reject requires remarks)</t>
         </is>
       </c>
       <c r="C21" s="49" t="n">
         <v>46226</v>
       </c>
       <c r="D21" s="49" t="n">
-        <v>46226</v>
+        <v>46247</v>
       </c>
       <c r="E21" s="24">
         <f>IF(OR(C21="",D21=""),"",NETWORKDAYS(C21,D21))</f>
@@ -2570,7 +2574,7 @@
       </c>
       <c r="I21" s="48" t="inlineStr">
         <is>
-          <t>File Leave for Member page exists with member selection, leave form, LWOP warning, attachment rules, confirm modal, and mock submit.</t>
+          <t>Review page calls live approveLeave / rejectLeave APIs with confirmation modals.</t>
         </is>
       </c>
     </row>
@@ -2582,14 +2586,14 @@
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Team leave calendar and upcoming approved leaves</t>
+          <t>Show clear approval details (who still needs to act)</t>
         </is>
       </c>
       <c r="C22" s="49" t="n">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="D22" s="49" t="n">
-        <v>46232</v>
+        <v>46244</v>
       </c>
       <c r="E22" s="24">
         <f>IF(OR(C22="",D22=""),"",NETWORKDAYS(C22,D22))</f>
@@ -2610,87 +2614,87 @@
       </c>
       <c r="I22" s="48" t="inlineStr">
         <is>
-          <t>Team Leave Calendar page (month/week views, filters, leave chips) and Upcoming Approved Leaves page are both built with mock data.</t>
+          <t>Changed: progress-bar UI removed. Shared Approval Details table + ApproverStatusBadge on employee/approver/admin request pages.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="50" t="inlineStr">
-        <is>
-          <t>5. Admin Features</t>
-        </is>
-      </c>
-      <c r="B23" s="50" t="inlineStr">
-        <is>
-          <t>Admin view of leave requests and request details</t>
-        </is>
-      </c>
-      <c r="C23" s="51" t="n">
+      <c r="A23" s="48" t="inlineStr">
+        <is>
+          <t>4. Approver / Team Features</t>
+        </is>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>File leave on behalf of a team member</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n">
+        <v>46226</v>
+      </c>
+      <c r="D23" s="49" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E23" s="24">
+        <f>IF(OR(C23="",D23=""),"",NETWORKDAYS(C23,D23))</f>
+        <v/>
+      </c>
+      <c r="F23" s="66" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G23" s="25">
+        <f>IF(F23="Completed",1,IF(F23="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H23" s="65">
+        <f>IF(C23="","",C23+MOD(5-WEEKDAY(C23,2),7))</f>
+        <v/>
+      </c>
+      <c r="I23" s="48" t="inlineStr">
+        <is>
+          <t>UI complete; holidays hook wired. Full live submit / member directory API still being finished.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="48" t="inlineStr">
+        <is>
+          <t>4. Approver / Team Features</t>
+        </is>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Team leave calendar and upcoming approved leaves</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n">
         <v>46232</v>
       </c>
-      <c r="D23" s="51" t="n">
+      <c r="D24" s="49" t="n">
         <v>46232</v>
       </c>
-      <c r="E23" s="27">
-        <f>IF(OR(C23="",D23=""),"",NETWORKDAYS(C23,D23))</f>
-        <v/>
-      </c>
-      <c r="F23" s="36" t="inlineStr">
+      <c r="E24" s="24">
+        <f>IF(OR(C24="",D24=""),"",NETWORKDAYS(C24,D24))</f>
+        <v/>
+      </c>
+      <c r="F24" s="36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="G23" s="28">
-        <f>IF(F23="Completed",1,IF(F23="In Progress",0.5,0))</f>
-        <v/>
-      </c>
-      <c r="H23" s="66">
-        <f>IF(C23="","",C23+MOD(5-WEEKDAY(C23,2),7))</f>
-        <v/>
-      </c>
-      <c r="I23" s="50" t="inlineStr">
-        <is>
-          <t>Admin Leave Requests list (pending/all tabs, filters, search, reminders) and detail/view/validate pages are all built with mock data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="50" t="inlineStr">
-        <is>
-          <t>5. Admin Features</t>
-        </is>
-      </c>
-      <c r="B24" s="50" t="inlineStr">
-        <is>
-          <t>Review vacation-to-sick leave conversion requests</t>
-        </is>
-      </c>
-      <c r="C24" s="51" t="n">
-        <v>46232</v>
-      </c>
-      <c r="D24" s="51" t="n">
-        <v>46232</v>
-      </c>
-      <c r="E24" s="27">
-        <f>IF(OR(C24="",D24=""),"",NETWORKDAYS(C24,D24))</f>
-        <v/>
-      </c>
-      <c r="F24" s="36" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="G24" s="28">
+      <c r="G24" s="25">
         <f>IF(F24="Completed",1,IF(F24="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H24" s="66">
+      <c r="H24" s="65">
         <f>IF(C24="","",C24+MOD(5-WEEKDAY(C24,2),7))</f>
         <v/>
       </c>
-      <c r="I24" s="50" t="inlineStr">
-        <is>
-          <t>Conversion review is handled via Admin Leave Validate page; conversion state visible on request detail/view pages.</t>
+      <c r="I24" s="48" t="inlineStr">
+        <is>
+          <t>Calendar + upcoming pages built. Still on mock calendar data until team-calendar API is connected.</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2706,7 @@
       </c>
       <c r="B25" s="50" t="inlineStr">
         <is>
-          <t>Manage leave balances and credit distribution</t>
+          <t>Admin view of leave requests and request details</t>
         </is>
       </c>
       <c r="C25" s="51" t="n">
@@ -2724,13 +2728,13 @@
         <f>IF(F25="Completed",1,IF(F25="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H25" s="66">
+      <c r="H25" s="67">
         <f>IF(C25="","",C25+MOD(5-WEEKDAY(C25,2),7))</f>
         <v/>
       </c>
       <c r="I25" s="50" t="inlineStr">
         <is>
-          <t>Admin Leave Balances page with filters, adjust-credits modal, and full distribution flows (annual, newly-regularized, parental, contractual) are built with mock data.</t>
+          <t>Admin Leave Requests list + detail/validate UIs built. Still mock data until admin API wiring.</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2746,7 @@
       </c>
       <c r="B26" s="50" t="inlineStr">
         <is>
-          <t>Administrative logs</t>
+          <t>Review vacation-to-sick leave conversion requests</t>
         </is>
       </c>
       <c r="C26" s="51" t="n">
@@ -2764,13 +2768,13 @@
         <f>IF(F26="Completed",1,IF(F26="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H26" s="66">
+      <c r="H26" s="67">
         <f>IF(C26="","",C26+MOD(5-WEEKDAY(C26,2),7))</f>
         <v/>
       </c>
       <c r="I26" s="50" t="inlineStr">
         <is>
-          <t>Admin Administrative Log page with search, filters, month-year picker, sorting, and pagination is built with mock data.</t>
+          <t>Conversion review via Admin Leave Validate page (UI). Live admin conversion API not wired yet.</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2786,7 @@
       </c>
       <c r="B27" s="50" t="inlineStr">
         <is>
-          <t>Monthly Attendance Report</t>
+          <t>Manage leave balances and credit distribution</t>
         </is>
       </c>
       <c r="C27" s="51" t="n">
@@ -2804,13 +2808,13 @@
         <f>IF(F27="Completed",1,IF(F27="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H27" s="66">
+      <c r="H27" s="67">
         <f>IF(C27="","",C27+MOD(5-WEEKDAY(C27,2),7))</f>
         <v/>
       </c>
       <c r="I27" s="50" t="inlineStr">
         <is>
-          <t>Report page with month/cut-off filters, employee multi-select, group filter, calendar grid, legend, print, and download. Uses mock data.</t>
+          <t>Balances + distribution flows (annual, newly-regularized, parental, contractual) built with mock data.</t>
         </is>
       </c>
     </row>
@@ -2822,14 +2826,14 @@
       </c>
       <c r="B28" s="50" t="inlineStr">
         <is>
-          <t>Leave Monetization Candidates report</t>
+          <t>Administrative logs</t>
         </is>
       </c>
       <c r="C28" s="51" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="D28" s="51" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="E28" s="27">
         <f>IF(OR(C28="",D28=""),"",NETWORKDAYS(C28,D28))</f>
@@ -2844,13 +2848,13 @@
         <f>IF(F28="Completed",1,IF(F28="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H28" s="66">
+      <c r="H28" s="67">
         <f>IF(C28="","",C28+MOD(5-WEEKDAY(C28,2),7))</f>
         <v/>
       </c>
       <c r="I28" s="50" t="inlineStr">
         <is>
-          <t>Report page with year filter, eligibility filters, sortable table, summary totals, print, and download. Uses mock data.</t>
+          <t>Admin Administrative Log UI built with mock data.</t>
         </is>
       </c>
     </row>
@@ -2862,14 +2866,14 @@
       </c>
       <c r="B29" s="50" t="inlineStr">
         <is>
-          <t>Employees with LWOP report</t>
+          <t>Monthly Attendance Report</t>
         </is>
       </c>
       <c r="C29" s="51" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="D29" s="51" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="E29" s="27">
         <f>IF(OR(C29="",D29=""),"",NETWORKDAYS(C29,D29))</f>
@@ -2884,13 +2888,13 @@
         <f>IF(F29="Completed",1,IF(F29="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H29" s="66">
+      <c r="H29" s="67">
         <f>IF(C29="","",C29+MOD(5-WEEKDAY(C29,2),7))</f>
         <v/>
       </c>
       <c r="I29" s="50" t="inlineStr">
         <is>
-          <t>Report page with year and group filters, sortable LWOP summary table, print, and download. Uses mock data.</t>
+          <t>Report UI built (filters, grid, print/download). Mock data until reports API.</t>
         </is>
       </c>
     </row>
@@ -2902,14 +2906,14 @@
       </c>
       <c r="B30" s="50" t="inlineStr">
         <is>
-          <t>Support other leave types (emergency, maternity, etc.) in the screens</t>
+          <t>Leave Monetization Candidates report</t>
         </is>
       </c>
       <c r="C30" s="51" t="n">
-        <v>46225</v>
+        <v>46233</v>
       </c>
       <c r="D30" s="51" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E30" s="27">
         <f>IF(OR(C30="",D30=""),"",NETWORKDAYS(C30,D30))</f>
@@ -2924,118 +2928,118 @@
         <f>IF(F30="Completed",1,IF(F30="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H30" s="66">
+      <c r="H30" s="67">
         <f>IF(C30="","",C30+MOD(5-WEEKDAY(C30,2),7))</f>
         <v/>
       </c>
       <c r="I30" s="50" t="inlineStr">
         <is>
-          <t>Emergency, PTB, Maternity/Paternity handled in employee/team filing and in admin screens. Monthly attendance report covers all leave categories including LWOP.</t>
+          <t>Report UI built. Mock data until reports API.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="67" t="inlineStr">
+      <c r="A31" s="50" t="inlineStr">
+        <is>
+          <t>5. Admin Features</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="inlineStr">
+        <is>
+          <t>Employees with LWOP report</t>
+        </is>
+      </c>
+      <c r="C31" s="51" t="n">
+        <v>46233</v>
+      </c>
+      <c r="D31" s="51" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E31" s="27">
+        <f>IF(OR(C31="",D31=""),"",NETWORKDAYS(C31,D31))</f>
+        <v/>
+      </c>
+      <c r="F31" s="36" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G31" s="28">
+        <f>IF(F31="Completed",1,IF(F31="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H31" s="67">
+        <f>IF(C31="","",C31+MOD(5-WEEKDAY(C31,2),7))</f>
+        <v/>
+      </c>
+      <c r="I31" s="50" t="inlineStr">
+        <is>
+          <t>Report UI built. Mock data until reports API.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="50" t="inlineStr">
+        <is>
+          <t>5. Admin Features</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="inlineStr">
+        <is>
+          <t>Support other leave types (emergency, maternity, etc.) in the screens</t>
+        </is>
+      </c>
+      <c r="C32" s="51" t="n">
+        <v>46225</v>
+      </c>
+      <c r="D32" s="51" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E32" s="27">
+        <f>IF(OR(C32="",D32=""),"",NETWORKDAYS(C32,D32))</f>
+        <v/>
+      </c>
+      <c r="F32" s="36" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G32" s="28">
+        <f>IF(F32="Completed",1,IF(F32="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H32" s="67">
+        <f>IF(C32="","",C32+MOD(5-WEEKDAY(C32,2),7))</f>
+        <v/>
+      </c>
+      <c r="I32" s="50" t="inlineStr">
+        <is>
+          <t>Emergency, PTB, Maternity/Paternity handled across filing and admin screens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="68" t="inlineStr">
         <is>
           <t>6. UI Polish &amp; Cleanup</t>
         </is>
       </c>
-      <c r="B31" s="67" t="inlineStr">
+      <c r="B33" s="68" t="inlineStr">
         <is>
           <t>Review and clean up global CSS (colors, fonts, spacing, typography)</t>
         </is>
       </c>
-      <c r="C31" s="68" t="n">
+      <c r="C33" s="69" t="n">
         <v>46233</v>
       </c>
-      <c r="D31" s="68" t="n">
-        <v>46242</v>
-      </c>
-      <c r="E31" s="30">
-        <f>IF(OR(C31="",D31=""),"",NETWORKDAYS(C31,D31))</f>
-        <v/>
-      </c>
-      <c r="F31" s="69" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="G31" s="31">
-        <f>IF(F31="Completed",1,IF(F31="In Progress",0.5,0))</f>
-        <v/>
-      </c>
-      <c r="H31" s="70">
-        <f>IF(C31="","",C31+MOD(5-WEEKDAY(C31,2),7))</f>
-        <v/>
-      </c>
-      <c r="I31" s="67" t="inlineStr">
-        <is>
-          <t>Currently in progress — checking index.css theme tokens, base styles, and consistency with Tailwind usage across screens.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="67" t="inlineStr">
-        <is>
-          <t>6. UI Polish &amp; Cleanup</t>
-        </is>
-      </c>
-      <c r="B32" s="67" t="inlineStr">
-        <is>
-          <t>Check and fix app shell layout (sidebar, top header, main content area)</t>
-        </is>
-      </c>
-      <c r="C32" s="68" t="n">
-        <v>46233</v>
-      </c>
-      <c r="D32" s="68" t="n">
-        <v>46242</v>
-      </c>
-      <c r="E32" s="30">
-        <f>IF(OR(C32="",D32=""),"",NETWORKDAYS(C32,D32))</f>
-        <v/>
-      </c>
-      <c r="F32" s="69" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="G32" s="31">
-        <f>IF(F32="Completed",1,IF(F32="In Progress",0.5,0))</f>
-        <v/>
-      </c>
-      <c r="H32" s="70">
-        <f>IF(C32="","",C32+MOD(5-WEEKDAY(C32,2),7))</f>
-        <v/>
-      </c>
-      <c r="I32" s="67" t="inlineStr">
-        <is>
-          <t>Currently in progress — reviewing AppLayout, collapsible sidebar, header alignment, and page padding/overflow behavior.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="67" t="inlineStr">
-        <is>
-          <t>6. UI Polish &amp; Cleanup</t>
-        </is>
-      </c>
-      <c r="B33" s="67" t="inlineStr">
-        <is>
-          <t>Standardize screen layouts (tables, filter bars, forms, and reports)</t>
-        </is>
-      </c>
-      <c r="C33" s="68" t="n">
-        <v>46233</v>
-      </c>
-      <c r="D33" s="68" t="n">
-        <v>46249</v>
+      <c r="D33" s="69" t="n">
+        <v>46256</v>
       </c>
       <c r="E33" s="30">
         <f>IF(OR(C33="",D33=""),"",NETWORKDAYS(C33,D33))</f>
         <v/>
       </c>
-      <c r="F33" s="69" t="inlineStr">
+      <c r="F33" s="66" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
@@ -3048,121 +3052,129 @@
         <f>IF(C33="","",C33+MOD(5-WEEKDAY(C33,2),7))</f>
         <v/>
       </c>
-      <c r="I33" s="67" t="inlineStr">
-        <is>
-          <t>Currently in progress — aligning filter control heights, table spacing, button placement, and responsive layout on list/form/report pages.</t>
+      <c r="I33" s="68" t="inlineStr">
+        <is>
+          <t>STILL IN PROGRESS as of 2026-08-13 — codebase review and CSS cleanup ongoing.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="56" t="inlineStr">
-        <is>
-          <t>7. Backend Integration (TBD)</t>
-        </is>
-      </c>
-      <c r="B34" s="56" t="inlineStr">
-        <is>
-          <t>Connect frontend to backend API (base connection and shared data types)</t>
-        </is>
-      </c>
-      <c r="C34" s="71" t="n">
-        <v>46226</v>
-      </c>
-      <c r="D34" s="71" t="n"/>
-      <c r="E34" s="33">
+      <c r="A34" s="68" t="inlineStr">
+        <is>
+          <t>6. UI Polish &amp; Cleanup</t>
+        </is>
+      </c>
+      <c r="B34" s="68" t="inlineStr">
+        <is>
+          <t>Check and fix app shell layout (sidebar, top header, main content area)</t>
+        </is>
+      </c>
+      <c r="C34" s="69" t="n">
+        <v>46233</v>
+      </c>
+      <c r="D34" s="69" t="n">
+        <v>46256</v>
+      </c>
+      <c r="E34" s="30">
         <f>IF(OR(C34="",D34=""),"",NETWORKDAYS(C34,D34))</f>
         <v/>
       </c>
-      <c r="F34" s="72" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G34" s="34">
+      <c r="F34" s="66" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G34" s="31">
         <f>IF(F34="Completed",1,IF(F34="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H34" s="73">
+      <c r="H34" s="70">
         <f>IF(C34="","",C34+MOD(5-WEEKDAY(C34,2),7))</f>
         <v/>
       </c>
-      <c r="I34" s="56" t="inlineStr">
-        <is>
-          <t>Duration TBD — frontend and backend work separately. Update Start/End when schedule is known.</t>
+      <c r="I34" s="68" t="inlineStr">
+        <is>
+          <t>STILL IN PROGRESS as of 2026-08-13 — AppLayout, sidebar, header, overflow, and content spacing under review.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="56" t="inlineStr">
-        <is>
-          <t>7. Backend Integration (TBD)</t>
-        </is>
-      </c>
-      <c r="B35" s="56" t="inlineStr">
-        <is>
-          <t>Use portal cookies / session to identify the user (no separate login page)</t>
-        </is>
-      </c>
-      <c r="C35" s="71" t="n">
-        <v>46226</v>
-      </c>
-      <c r="D35" s="71" t="n"/>
-      <c r="E35" s="33">
+      <c r="A35" s="68" t="inlineStr">
+        <is>
+          <t>6. UI Polish &amp; Cleanup</t>
+        </is>
+      </c>
+      <c r="B35" s="68" t="inlineStr">
+        <is>
+          <t>Standardize screen layouts (tables, filter bars, forms, and reports)</t>
+        </is>
+      </c>
+      <c r="C35" s="69" t="n">
+        <v>46233</v>
+      </c>
+      <c r="D35" s="69" t="n">
+        <v>46256</v>
+      </c>
+      <c r="E35" s="30">
         <f>IF(OR(C35="",D35=""),"",NETWORKDAYS(C35,D35))</f>
         <v/>
       </c>
-      <c r="F35" s="72" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G35" s="34">
+      <c r="F35" s="66" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G35" s="31">
         <f>IF(F35="Completed",1,IF(F35="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H35" s="73">
+      <c r="H35" s="70">
         <f>IF(C35="","",C35+MOD(5-WEEKDAY(C35,2),7))</f>
         <v/>
       </c>
-      <c r="I35" s="56" t="inlineStr">
-        <is>
-          <t>Duration TBD — frontend and backend work separately. Update Start/End when schedule is known. Agreed with backend: cookies/session — no login screen.</t>
+      <c r="I35" s="68" t="inlineStr">
+        <is>
+          <t>STILL IN PROGRESS as of 2026-08-13 — table/filter/form consistency and empty states being aligned across pages.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="56" t="inlineStr">
-        <is>
-          <t>7. Backend Integration (TBD)</t>
-        </is>
-      </c>
-      <c r="B36" s="56" t="inlineStr">
-        <is>
-          <t>Connect employee leave screens to live API (file, history, cancel, edit)</t>
-        </is>
-      </c>
-      <c r="C36" s="71" t="n"/>
-      <c r="D36" s="71" t="n"/>
-      <c r="E36" s="33">
+      <c r="A36" s="68" t="inlineStr">
+        <is>
+          <t>6. UI Polish &amp; Cleanup</t>
+        </is>
+      </c>
+      <c r="B36" s="68" t="inlineStr">
+        <is>
+          <t>Extract shared leave UI and remove unused placeholder code</t>
+        </is>
+      </c>
+      <c r="C36" s="69" t="n">
+        <v>46240</v>
+      </c>
+      <c r="D36" s="69" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E36" s="30">
         <f>IF(OR(C36="",D36=""),"",NETWORKDAYS(C36,D36))</f>
         <v/>
       </c>
-      <c r="F36" s="72" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G36" s="34">
+      <c r="F36" s="36" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G36" s="31">
         <f>IF(F36="Completed",1,IF(F36="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H36" s="73">
+      <c r="H36" s="70">
         <f>IF(C36="","",C36+MOD(5-WEEKDAY(C36,2),7))</f>
         <v/>
       </c>
-      <c r="I36" s="56" t="inlineStr">
-        <is>
-          <t>Duration TBD — frontend and backend work separately. Update Start/End when schedule is known.</t>
+      <c r="I36" s="68" t="inlineStr">
+        <is>
+          <t>Shared leave components added; PagePlaceholder removed; EmptyState / TableEmptyRow rolled out.</t>
         </is>
       </c>
     </row>
@@ -3174,31 +3186,35 @@
       </c>
       <c r="B37" s="56" t="inlineStr">
         <is>
-          <t>Connect approver / team screens to live API (inbox, approve, reject)</t>
-        </is>
-      </c>
-      <c r="C37" s="71" t="n"/>
-      <c r="D37" s="71" t="n"/>
+          <t>Connect frontend to backend API (base connection and shared data types)</t>
+        </is>
+      </c>
+      <c r="C37" s="71" t="n">
+        <v>46245</v>
+      </c>
+      <c r="D37" s="71" t="n">
+        <v>46247</v>
+      </c>
       <c r="E37" s="33">
         <f>IF(OR(C37="",D37=""),"",NETWORKDAYS(C37,D37))</f>
         <v/>
       </c>
-      <c r="F37" s="72" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="F37" s="36" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G37" s="34">
         <f>IF(F37="Completed",1,IF(F37="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H37" s="73">
+      <c r="H37" s="72">
         <f>IF(C37="","",C37+MOD(5-WEEKDAY(C37,2),7))</f>
         <v/>
       </c>
       <c r="I37" s="56" t="inlineStr">
         <is>
-          <t>Duration TBD — frontend and backend work separately. Update Start/End when schedule is known.</t>
+          <t>Axios client (/api), ApiError + 401 handling, typed API modules, and SWR provider/hooks are in place.</t>
         </is>
       </c>
     </row>
@@ -3210,31 +3226,35 @@
       </c>
       <c r="B38" s="56" t="inlineStr">
         <is>
-          <t>Connect admin screens to live API (balances, conversion, reports)</t>
-        </is>
-      </c>
-      <c r="C38" s="71" t="n"/>
-      <c r="D38" s="71" t="n"/>
+          <t>Use portal cookies / session to identify the user (no separate login page)</t>
+        </is>
+      </c>
+      <c r="C38" s="71" t="n">
+        <v>46245</v>
+      </c>
+      <c r="D38" s="71" t="n">
+        <v>46247</v>
+      </c>
       <c r="E38" s="33">
         <f>IF(OR(C38="",D38=""),"",NETWORKDAYS(C38,D38))</f>
         <v/>
       </c>
-      <c r="F38" s="72" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="F38" s="66" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G38" s="34">
         <f>IF(F38="Completed",1,IF(F38="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H38" s="73">
+      <c r="H38" s="72">
         <f>IF(C38="","",C38+MOD(5-WEEKDAY(C38,2),7))</f>
         <v/>
       </c>
       <c r="I38" s="56" t="inlineStr">
         <is>
-          <t>Duration TBD — frontend and backend work separately. Update Start/End when schedule is known.</t>
+          <t>Auth bootstraps from userID cookie + GET /api/me. Dev-only Employee ID entry (/login) for local testing — production remains cookie/portal session.</t>
         </is>
       </c>
     </row>
@@ -3246,145 +3266,147 @@
       </c>
       <c r="B39" s="56" t="inlineStr">
         <is>
-          <t>Joint frontend–backend smoke check once APIs are available</t>
-        </is>
-      </c>
-      <c r="C39" s="71" t="n"/>
-      <c r="D39" s="71" t="n"/>
+          <t>Connect employee leave screens to live API (file, history, cancel, edit)</t>
+        </is>
+      </c>
+      <c r="C39" s="71" t="n">
+        <v>46245</v>
+      </c>
+      <c r="D39" s="71" t="n">
+        <v>46247</v>
+      </c>
       <c r="E39" s="33">
         <f>IF(OR(C39="",D39=""),"",NETWORKDAYS(C39,D39))</f>
         <v/>
       </c>
-      <c r="F39" s="72" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="F39" s="66" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G39" s="34">
         <f>IF(F39="Completed",1,IF(F39="In Progress",0.5,0))</f>
         <v/>
       </c>
-      <c r="H39" s="73">
+      <c r="H39" s="72">
         <f>IF(C39="","",C39+MOD(5-WEEKDAY(C39,2),7))</f>
         <v/>
       </c>
       <c r="I39" s="56" t="inlineStr">
         <is>
+          <t>Dashboard, activity log, file/edit/cancel/convert, and details are on live APIs. Continue hardening error handling and edge cases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="56" t="inlineStr">
+        <is>
+          <t>7. Backend Integration (TBD)</t>
+        </is>
+      </c>
+      <c r="B40" s="56" t="inlineStr">
+        <is>
+          <t>Connect approver / team screens to live API (inbox, approve, reject)</t>
+        </is>
+      </c>
+      <c r="C40" s="71" t="n">
+        <v>46245</v>
+      </c>
+      <c r="D40" s="71" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E40" s="33">
+        <f>IF(OR(C40="",D40=""),"",NETWORKDAYS(C40,D40))</f>
+        <v/>
+      </c>
+      <c r="F40" s="66" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G40" s="34">
+        <f>IF(F40="Completed",1,IF(F40="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H40" s="72">
+        <f>IF(C40="","",C40+MOD(5-WEEKDAY(C40,2),7))</f>
+        <v/>
+      </c>
+      <c r="I40" s="56" t="inlineStr">
+        <is>
+          <t>Approvals inbox + approve/reject live. Team calendar / file-for-member still need fuller API coverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="56" t="inlineStr">
+        <is>
+          <t>7. Backend Integration (TBD)</t>
+        </is>
+      </c>
+      <c r="B41" s="56" t="inlineStr">
+        <is>
+          <t>Connect admin screens to live API (balances, conversion, reports)</t>
+        </is>
+      </c>
+      <c r="C41" s="71" t="n"/>
+      <c r="D41" s="71" t="n"/>
+      <c r="E41" s="33">
+        <f>IF(OR(C41="",D41=""),"",NETWORKDAYS(C41,D41))</f>
+        <v/>
+      </c>
+      <c r="F41" s="73" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G41" s="34">
+        <f>IF(F41="Completed",1,IF(F41="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H41" s="72">
+        <f>IF(C41="","",C41+MOD(5-WEEKDAY(C41,2),7))</f>
+        <v/>
+      </c>
+      <c r="I41" s="56" t="inlineStr">
+        <is>
+          <t>Duration TBD — frontend and backend work separately. Update Start/End when schedule is known. Admin screens still use mock data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="56" t="inlineStr">
+        <is>
+          <t>7. Backend Integration (TBD)</t>
+        </is>
+      </c>
+      <c r="B42" s="56" t="inlineStr">
+        <is>
+          <t>Joint frontend–backend smoke check once APIs are available</t>
+        </is>
+      </c>
+      <c r="C42" s="71" t="n"/>
+      <c r="D42" s="71" t="n"/>
+      <c r="E42" s="33">
+        <f>IF(OR(C42="",D42=""),"",NETWORKDAYS(C42,D42))</f>
+        <v/>
+      </c>
+      <c r="F42" s="73" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G42" s="34">
+        <f>IF(F42="Completed",1,IF(F42="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H42" s="72">
+        <f>IF(C42="","",C42+MOD(5-WEEKDAY(C42,2),7))</f>
+        <v/>
+      </c>
+      <c r="I42" s="56" t="inlineStr">
+        <is>
           <t>Duration TBD — frontend and backend work separately. Update Start/End when schedule is known.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="57" t="inlineStr">
-        <is>
-          <t>8. Testing (after development)</t>
-        </is>
-      </c>
-      <c r="B40" s="57" t="inlineStr">
-        <is>
-          <t>Employee flow testing (file, edit, cancel, view history)</t>
-        </is>
-      </c>
-      <c r="C40" s="74" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D40" s="74" t="n"/>
-      <c r="E40" s="36">
-        <f>IF(OR(C40="",D40=""),"",NETWORKDAYS(C40,D40))</f>
-        <v/>
-      </c>
-      <c r="F40" s="72" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G40" s="37">
-        <f>IF(F40="Completed",1,IF(F40="In Progress",0.5,0))</f>
-        <v/>
-      </c>
-      <c r="H40" s="75">
-        <f>IF(C40="","",C40+MOD(5-WEEKDAY(C40,2),7))</f>
-        <v/>
-      </c>
-      <c r="I40" s="57" t="inlineStr">
-        <is>
-          <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="57" t="inlineStr">
-        <is>
-          <t>8. Testing (after development)</t>
-        </is>
-      </c>
-      <c r="B41" s="57" t="inlineStr">
-        <is>
-          <t>Approver flow testing (approve, reject, team views)</t>
-        </is>
-      </c>
-      <c r="C41" s="74" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D41" s="74" t="n"/>
-      <c r="E41" s="36">
-        <f>IF(OR(C41="",D41=""),"",NETWORKDAYS(C41,D41))</f>
-        <v/>
-      </c>
-      <c r="F41" s="72" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G41" s="37">
-        <f>IF(F41="Completed",1,IF(F41="In Progress",0.5,0))</f>
-        <v/>
-      </c>
-      <c r="H41" s="75">
-        <f>IF(C41="","",C41+MOD(5-WEEKDAY(C41,2),7))</f>
-        <v/>
-      </c>
-      <c r="I41" s="57" t="inlineStr">
-        <is>
-          <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="57" t="inlineStr">
-        <is>
-          <t>8. Testing (after development)</t>
-        </is>
-      </c>
-      <c r="B42" s="57" t="inlineStr">
-        <is>
-          <t>Admin flow testing (balances, conversion, reports)</t>
-        </is>
-      </c>
-      <c r="C42" s="74" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D42" s="74" t="n"/>
-      <c r="E42" s="36">
-        <f>IF(OR(C42="",D42=""),"",NETWORKDAYS(C42,D42))</f>
-        <v/>
-      </c>
-      <c r="F42" s="72" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G42" s="37">
-        <f>IF(F42="Completed",1,IF(F42="In Progress",0.5,0))</f>
-        <v/>
-      </c>
-      <c r="H42" s="75">
-        <f>IF(C42="","",C42+MOD(5-WEEKDAY(C42,2),7))</f>
-        <v/>
-      </c>
-      <c r="I42" s="57" t="inlineStr">
-        <is>
-          <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3418,7 @@
       </c>
       <c r="B43" s="57" t="inlineStr">
         <is>
-          <t>Mobile / responsive check on common screens</t>
+          <t>Employee flow testing (file, edit, cancel, view history)</t>
         </is>
       </c>
       <c r="C43" s="74" t="n">
@@ -3407,7 +3429,7 @@
         <f>IF(OR(C43="",D43=""),"",NETWORKDAYS(C43,D43))</f>
         <v/>
       </c>
-      <c r="F43" s="72" t="inlineStr">
+      <c r="F43" s="73" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -3434,7 +3456,7 @@
       </c>
       <c r="B44" s="57" t="inlineStr">
         <is>
-          <t>Fix issues found during testing</t>
+          <t>Approver flow testing (approve, reject, team views)</t>
         </is>
       </c>
       <c r="C44" s="74" t="n">
@@ -3445,7 +3467,7 @@
         <f>IF(OR(C44="",D44=""),"",NETWORKDAYS(C44,D44))</f>
         <v/>
       </c>
-      <c r="F44" s="72" t="inlineStr">
+      <c r="F44" s="73" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -3465,132 +3487,246 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="58" t="inlineStr">
+      <c r="A45" s="57" t="inlineStr">
+        <is>
+          <t>8. Testing (after development)</t>
+        </is>
+      </c>
+      <c r="B45" s="57" t="inlineStr">
+        <is>
+          <t>Admin flow testing (balances, conversion, reports)</t>
+        </is>
+      </c>
+      <c r="C45" s="74" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D45" s="74" t="n"/>
+      <c r="E45" s="36">
+        <f>IF(OR(C45="",D45=""),"",NETWORKDAYS(C45,D45))</f>
+        <v/>
+      </c>
+      <c r="F45" s="73" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G45" s="37">
+        <f>IF(F45="Completed",1,IF(F45="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H45" s="75">
+        <f>IF(C45="","",C45+MOD(5-WEEKDAY(C45,2),7))</f>
+        <v/>
+      </c>
+      <c r="I45" s="57" t="inlineStr">
+        <is>
+          <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="57" t="inlineStr">
+        <is>
+          <t>8. Testing (after development)</t>
+        </is>
+      </c>
+      <c r="B46" s="57" t="inlineStr">
+        <is>
+          <t>Mobile / responsive check on common screens</t>
+        </is>
+      </c>
+      <c r="C46" s="74" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D46" s="74" t="n"/>
+      <c r="E46" s="36">
+        <f>IF(OR(C46="",D46=""),"",NETWORKDAYS(C46,D46))</f>
+        <v/>
+      </c>
+      <c r="F46" s="73" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G46" s="37">
+        <f>IF(F46="Completed",1,IF(F46="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H46" s="75">
+        <f>IF(C46="","",C46+MOD(5-WEEKDAY(C46,2),7))</f>
+        <v/>
+      </c>
+      <c r="I46" s="57" t="inlineStr">
+        <is>
+          <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="57" t="inlineStr">
+        <is>
+          <t>8. Testing (after development)</t>
+        </is>
+      </c>
+      <c r="B47" s="57" t="inlineStr">
+        <is>
+          <t>Fix issues found during testing</t>
+        </is>
+      </c>
+      <c r="C47" s="74" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D47" s="74" t="n"/>
+      <c r="E47" s="36">
+        <f>IF(OR(C47="",D47=""),"",NETWORKDAYS(C47,D47))</f>
+        <v/>
+      </c>
+      <c r="F47" s="73" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G47" s="37">
+        <f>IF(F47="Completed",1,IF(F47="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H47" s="75">
+        <f>IF(C47="","",C47+MOD(5-WEEKDAY(C47,2),7))</f>
+        <v/>
+      </c>
+      <c r="I47" s="57" t="inlineStr">
+        <is>
+          <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="58" t="inlineStr">
         <is>
           <t>9. Documentation (after development)</t>
         </is>
       </c>
-      <c r="B45" s="58" t="inlineStr">
+      <c r="B48" s="58" t="inlineStr">
         <is>
           <t>Finalize frontend guide for the team (FRONTEND.md)</t>
         </is>
       </c>
-      <c r="C45" s="76" t="n">
+      <c r="C48" s="76" t="n">
         <v>46266</v>
       </c>
-      <c r="D45" s="76" t="n"/>
-      <c r="E45" s="39">
-        <f>IF(OR(C45="",D45=""),"",NETWORKDAYS(C45,D45))</f>
-        <v/>
-      </c>
-      <c r="F45" s="72" t="inlineStr">
+      <c r="D48" s="76" t="n"/>
+      <c r="E48" s="39">
+        <f>IF(OR(C48="",D48=""),"",NETWORKDAYS(C48,D48))</f>
+        <v/>
+      </c>
+      <c r="F48" s="73" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G45" s="40">
-        <f>IF(F45="Completed",1,IF(F45="In Progress",0.5,0))</f>
-        <v/>
-      </c>
-      <c r="H45" s="77">
-        <f>IF(C45="","",C45+MOD(5-WEEKDAY(C45,2),7))</f>
-        <v/>
-      </c>
-      <c r="I45" s="58" t="inlineStr">
+      <c r="G48" s="40">
+        <f>IF(F48="Completed",1,IF(F48="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H48" s="77">
+        <f>IF(C48="","",C48+MOD(5-WEEKDAY(C48,2),7))</f>
+        <v/>
+      </c>
+      <c r="I48" s="58" t="inlineStr">
         <is>
           <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="58" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="58" t="inlineStr">
         <is>
           <t>9. Documentation (after development)</t>
         </is>
       </c>
-      <c r="B46" s="58" t="inlineStr">
+      <c r="B49" s="58" t="inlineStr">
         <is>
           <t>Prepare short demo / walkthrough notes for stakeholders</t>
         </is>
       </c>
-      <c r="C46" s="76" t="n">
+      <c r="C49" s="76" t="n">
         <v>46266</v>
       </c>
-      <c r="D46" s="76" t="n"/>
-      <c r="E46" s="39">
-        <f>IF(OR(C46="",D46=""),"",NETWORKDAYS(C46,D46))</f>
-        <v/>
-      </c>
-      <c r="F46" s="72" t="inlineStr">
+      <c r="D49" s="76" t="n"/>
+      <c r="E49" s="39">
+        <f>IF(OR(C49="",D49=""),"",NETWORKDAYS(C49,D49))</f>
+        <v/>
+      </c>
+      <c r="F49" s="73" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G46" s="40">
-        <f>IF(F46="Completed",1,IF(F46="In Progress",0.5,0))</f>
-        <v/>
-      </c>
-      <c r="H46" s="77">
-        <f>IF(C46="","",C46+MOD(5-WEEKDAY(C46,2),7))</f>
-        <v/>
-      </c>
-      <c r="I46" s="58" t="inlineStr">
+      <c r="G49" s="40">
+        <f>IF(F49="Completed",1,IF(F49="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H49" s="77">
+        <f>IF(C49="","",C49+MOD(5-WEEKDAY(C49,2),7))</f>
+        <v/>
+      </c>
+      <c r="I49" s="58" t="inlineStr">
         <is>
           <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="58" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="58" t="inlineStr">
         <is>
           <t>9. Documentation (after development)</t>
         </is>
       </c>
-      <c r="B47" s="58" t="inlineStr">
+      <c r="B50" s="58" t="inlineStr">
         <is>
           <t>Handover checklist (how to run, deploy, and who owns what)</t>
         </is>
       </c>
-      <c r="C47" s="76" t="n">
+      <c r="C50" s="76" t="n">
         <v>46266</v>
       </c>
-      <c r="D47" s="76" t="n"/>
-      <c r="E47" s="39">
-        <f>IF(OR(C47="",D47=""),"",NETWORKDAYS(C47,D47))</f>
-        <v/>
-      </c>
-      <c r="F47" s="72" t="inlineStr">
+      <c r="D50" s="76" t="n"/>
+      <c r="E50" s="39">
+        <f>IF(OR(C50="",D50=""),"",NETWORKDAYS(C50,D50))</f>
+        <v/>
+      </c>
+      <c r="F50" s="73" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G47" s="40">
-        <f>IF(F47="Completed",1,IF(F47="In Progress",0.5,0))</f>
-        <v/>
-      </c>
-      <c r="H47" s="77">
-        <f>IF(C47="","",C47+MOD(5-WEEKDAY(C47,2),7))</f>
-        <v/>
-      </c>
-      <c r="I47" s="58" t="inlineStr">
+      <c r="G50" s="40">
+        <f>IF(F50="Completed",1,IF(F50="In Progress",0.5,0))</f>
+        <v/>
+      </c>
+      <c r="H50" s="77">
+        <f>IF(C50="","",C50+MOD(5-WEEKDAY(C50,2),7))</f>
+        <v/>
+      </c>
+      <c r="I50" s="58" t="inlineStr">
         <is>
           <t>Starts after development. End of August commitment covers development only — dates TBD.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Commitment: frontend DEVELOPMENT finished by end of August (weekdays = NETWORKDAYS). Backend Integration has TBD end dates (teams work separately — fill dates when known). Testing and Documentation start after development (from Sep 2026); end dates TBD. No login page — portal cookies/session with backend.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I47"/>
+  <autoFilter ref="A1:I50"/>
   <mergeCells count="1">
-    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A52:I52"/>
   </mergeCells>
-  <conditionalFormatting sqref="G2:G47">
+  <conditionalFormatting sqref="G2:G50">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -3603,7 +3739,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="F2:F50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Not Started,In Progress,Completed,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3657,7 +3793,7 @@
     <row r="6">
       <c r="A6" s="78" t="inlineStr">
         <is>
-          <t>Backend Integration is listed with TBD dates — teams work separately for now.</t>
+          <t>Backend Integration is underway (employee + key approver). Admin APIs and remaining team screens still TBD.</t>
         </is>
       </c>
     </row>
